--- a/ANGO_Model.xlsx
+++ b/ANGO_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Health Care\MedTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27AB45B-C8EC-4CA8-9BAA-22512CA30D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB96907A-6321-435C-B6C9-CDCC1F58C5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,6 @@
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
-    <externalReference r:id="rId10"/>
   </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
@@ -96,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="1366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="1367">
   <si>
     <t>Master</t>
   </si>
@@ -4268,7 +4267,10 @@
     <t>Mar.</t>
   </si>
   <si>
-    <t>12/6/25</t>
+    <t>Q2'26</t>
+  </si>
+  <si>
+    <t>1/10/2025</t>
   </si>
 </sst>
 </file>
@@ -4635,7 +4637,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4762,7 +4764,6 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
@@ -4794,10 +4795,10 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -9252,6 +9253,56 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>6402</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>11205</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98AE2562-82BC-5F5D-CCF1-53BCCFDD7135}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="4025" r="3979"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3592284" y="560293"/>
+          <a:ext cx="1808951" cy="1266265"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>52</xdr:col>
@@ -9355,7 +9406,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -10100,46 +10151,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Notes | Quant Analysis"/>
-      <sheetName val="M&amp;A"/>
-      <sheetName val="Management"/>
-      <sheetName val="Markets | Product Lines"/>
-      <sheetName val="Debt Schedule"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="AY1" t="str">
-            <v>Q1 2021</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="188">
-          <cell r="I188" t="str">
-            <v>Notes:</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Jacob H" id="{EF8FC050-EB94-4F9B-97D0-A36CD00FA61C}" userId="6fdd6cd1f6a5d55a" providerId="Windows Live"/>
@@ -10701,12 +10712,12 @@
         <v>3</v>
       </c>
       <c r="C5" s="45">
-        <v>13.33</v>
+        <v>9.99</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>1365</v>
-      </c>
-      <c r="F5" s="69"/>
+        <v>1366</v>
+      </c>
+      <c r="F5" s="68"/>
     </row>
     <row r="6" spans="1:18">
       <c r="B6" s="1" t="s">
@@ -10716,17 +10727,17 @@
         <v>41.19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1357</v>
-      </c>
-      <c r="F6" s="69"/>
+        <v>1365</v>
+      </c>
+      <c r="F6" s="68"/>
     </row>
     <row r="7" spans="1:18" ht="15">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="70">
+      <c r="C7" s="69">
         <f>C5*C6</f>
-        <v>549.06269999999995</v>
+        <v>411.48809999999997</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>6</v>
@@ -10737,12 +10748,12 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="72">
+      <c r="C8" s="71">
         <f>38.76</f>
         <v>38.76</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>8</v>
@@ -10755,11 +10766,11 @@
       <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="71">
+      <c r="C9" s="70">
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>11</v>
@@ -10774,7 +10785,7 @@
       </c>
       <c r="C10" s="45">
         <f>C7-C8+C9</f>
-        <v>510.30269999999996</v>
+        <v>372.72809999999998</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>14</v>
@@ -11452,54 +11463,54 @@
       <c r="Y93" s="57"/>
     </row>
     <row r="94" spans="3:28">
-      <c r="D94" s="82" t="s">
+      <c r="D94" s="80" t="s">
         <v>120</v>
       </c>
-      <c r="E94" s="82"/>
-      <c r="F94" s="82"/>
-      <c r="G94" s="82"/>
-      <c r="H94" s="82"/>
-      <c r="I94" s="82"/>
-      <c r="J94" s="82"/>
-      <c r="K94" s="82"/>
-      <c r="L94" s="82"/>
-      <c r="M94" s="82"/>
-      <c r="N94" s="82"/>
-      <c r="O94" s="82"/>
-      <c r="P94" s="82"/>
-      <c r="Q94" s="82"/>
-      <c r="R94" s="82"/>
-      <c r="S94" s="82"/>
-      <c r="T94" s="82"/>
-      <c r="U94" s="82"/>
-      <c r="V94" s="82"/>
-      <c r="W94" s="82"/>
-      <c r="X94" s="82"/>
-      <c r="Y94" s="82"/>
+      <c r="E94" s="80"/>
+      <c r="F94" s="80"/>
+      <c r="G94" s="80"/>
+      <c r="H94" s="80"/>
+      <c r="I94" s="80"/>
+      <c r="J94" s="80"/>
+      <c r="K94" s="80"/>
+      <c r="L94" s="80"/>
+      <c r="M94" s="80"/>
+      <c r="N94" s="80"/>
+      <c r="O94" s="80"/>
+      <c r="P94" s="80"/>
+      <c r="Q94" s="80"/>
+      <c r="R94" s="80"/>
+      <c r="S94" s="80"/>
+      <c r="T94" s="80"/>
+      <c r="U94" s="80"/>
+      <c r="V94" s="80"/>
+      <c r="W94" s="80"/>
+      <c r="X94" s="80"/>
+      <c r="Y94" s="80"/>
     </row>
     <row r="95" spans="3:28">
-      <c r="D95" s="82"/>
-      <c r="E95" s="82"/>
-      <c r="F95" s="82"/>
-      <c r="G95" s="82"/>
-      <c r="H95" s="82"/>
-      <c r="I95" s="82"/>
-      <c r="J95" s="82"/>
-      <c r="K95" s="82"/>
-      <c r="L95" s="82"/>
-      <c r="M95" s="82"/>
-      <c r="N95" s="82"/>
-      <c r="O95" s="82"/>
-      <c r="P95" s="82"/>
-      <c r="Q95" s="82"/>
-      <c r="R95" s="82"/>
-      <c r="S95" s="82"/>
-      <c r="T95" s="82"/>
-      <c r="U95" s="82"/>
-      <c r="V95" s="82"/>
-      <c r="W95" s="82"/>
-      <c r="X95" s="82"/>
-      <c r="Y95" s="82"/>
+      <c r="D95" s="80"/>
+      <c r="E95" s="80"/>
+      <c r="F95" s="80"/>
+      <c r="G95" s="80"/>
+      <c r="H95" s="80"/>
+      <c r="I95" s="80"/>
+      <c r="J95" s="80"/>
+      <c r="K95" s="80"/>
+      <c r="L95" s="80"/>
+      <c r="M95" s="80"/>
+      <c r="N95" s="80"/>
+      <c r="O95" s="80"/>
+      <c r="P95" s="80"/>
+      <c r="Q95" s="80"/>
+      <c r="R95" s="80"/>
+      <c r="S95" s="80"/>
+      <c r="T95" s="80"/>
+      <c r="U95" s="80"/>
+      <c r="V95" s="80"/>
+      <c r="W95" s="80"/>
+      <c r="X95" s="80"/>
+      <c r="Y95" s="80"/>
     </row>
     <row r="96" spans="3:28">
       <c r="D96" s="81" t="s">
@@ -11567,54 +11578,54 @@
       </c>
     </row>
     <row r="101" spans="2:48">
-      <c r="D101" s="82" t="s">
+      <c r="D101" s="80" t="s">
         <v>125</v>
       </c>
-      <c r="E101" s="82"/>
-      <c r="F101" s="82"/>
-      <c r="G101" s="82"/>
-      <c r="H101" s="82"/>
-      <c r="I101" s="82"/>
-      <c r="J101" s="82"/>
-      <c r="K101" s="82"/>
-      <c r="L101" s="82"/>
-      <c r="M101" s="82"/>
-      <c r="N101" s="82"/>
-      <c r="O101" s="82"/>
-      <c r="P101" s="82"/>
-      <c r="Q101" s="82"/>
-      <c r="R101" s="82"/>
-      <c r="S101" s="82"/>
-      <c r="T101" s="82"/>
-      <c r="U101" s="82"/>
-      <c r="V101" s="82"/>
-      <c r="W101" s="82"/>
-      <c r="X101" s="82"/>
-      <c r="Y101" s="82"/>
+      <c r="E101" s="80"/>
+      <c r="F101" s="80"/>
+      <c r="G101" s="80"/>
+      <c r="H101" s="80"/>
+      <c r="I101" s="80"/>
+      <c r="J101" s="80"/>
+      <c r="K101" s="80"/>
+      <c r="L101" s="80"/>
+      <c r="M101" s="80"/>
+      <c r="N101" s="80"/>
+      <c r="O101" s="80"/>
+      <c r="P101" s="80"/>
+      <c r="Q101" s="80"/>
+      <c r="R101" s="80"/>
+      <c r="S101" s="80"/>
+      <c r="T101" s="80"/>
+      <c r="U101" s="80"/>
+      <c r="V101" s="80"/>
+      <c r="W101" s="80"/>
+      <c r="X101" s="80"/>
+      <c r="Y101" s="80"/>
     </row>
     <row r="102" spans="2:48">
-      <c r="D102" s="82"/>
-      <c r="E102" s="82"/>
-      <c r="F102" s="82"/>
-      <c r="G102" s="82"/>
-      <c r="H102" s="82"/>
-      <c r="I102" s="82"/>
-      <c r="J102" s="82"/>
-      <c r="K102" s="82"/>
-      <c r="L102" s="82"/>
-      <c r="M102" s="82"/>
-      <c r="N102" s="82"/>
-      <c r="O102" s="82"/>
-      <c r="P102" s="82"/>
-      <c r="Q102" s="82"/>
-      <c r="R102" s="82"/>
-      <c r="S102" s="82"/>
-      <c r="T102" s="82"/>
-      <c r="U102" s="82"/>
-      <c r="V102" s="82"/>
-      <c r="W102" s="82"/>
-      <c r="X102" s="82"/>
-      <c r="Y102" s="82"/>
+      <c r="D102" s="80"/>
+      <c r="E102" s="80"/>
+      <c r="F102" s="80"/>
+      <c r="G102" s="80"/>
+      <c r="H102" s="80"/>
+      <c r="I102" s="80"/>
+      <c r="J102" s="80"/>
+      <c r="K102" s="80"/>
+      <c r="L102" s="80"/>
+      <c r="M102" s="80"/>
+      <c r="N102" s="80"/>
+      <c r="O102" s="80"/>
+      <c r="P102" s="80"/>
+      <c r="Q102" s="80"/>
+      <c r="R102" s="80"/>
+      <c r="S102" s="80"/>
+      <c r="T102" s="80"/>
+      <c r="U102" s="80"/>
+      <c r="V102" s="80"/>
+      <c r="W102" s="80"/>
+      <c r="X102" s="80"/>
+      <c r="Y102" s="80"/>
     </row>
     <row r="103" spans="2:48">
       <c r="D103" s="81" t="s">
@@ -11844,155 +11855,155 @@
       <c r="C117" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D117" s="82" t="s">
+      <c r="D117" s="80" t="s">
         <v>138</v>
       </c>
-      <c r="E117" s="82"/>
-      <c r="F117" s="82"/>
-      <c r="G117" s="82"/>
-      <c r="H117" s="82"/>
-      <c r="I117" s="82"/>
-      <c r="J117" s="82"/>
-      <c r="K117" s="82"/>
-      <c r="L117" s="82"/>
-      <c r="M117" s="82"/>
-      <c r="N117" s="82"/>
-      <c r="O117" s="82"/>
-      <c r="P117" s="82"/>
-      <c r="Q117" s="82"/>
-      <c r="R117" s="82"/>
-      <c r="S117" s="82"/>
-      <c r="T117" s="82"/>
-      <c r="U117" s="82"/>
-      <c r="V117" s="82"/>
-      <c r="W117" s="82"/>
-      <c r="X117" s="82"/>
-      <c r="Y117" s="82"/>
+      <c r="E117" s="80"/>
+      <c r="F117" s="80"/>
+      <c r="G117" s="80"/>
+      <c r="H117" s="80"/>
+      <c r="I117" s="80"/>
+      <c r="J117" s="80"/>
+      <c r="K117" s="80"/>
+      <c r="L117" s="80"/>
+      <c r="M117" s="80"/>
+      <c r="N117" s="80"/>
+      <c r="O117" s="80"/>
+      <c r="P117" s="80"/>
+      <c r="Q117" s="80"/>
+      <c r="R117" s="80"/>
+      <c r="S117" s="80"/>
+      <c r="T117" s="80"/>
+      <c r="U117" s="80"/>
+      <c r="V117" s="80"/>
+      <c r="W117" s="80"/>
+      <c r="X117" s="80"/>
+      <c r="Y117" s="80"/>
     </row>
     <row r="118" spans="3:27">
-      <c r="D118" s="82"/>
-      <c r="E118" s="82"/>
-      <c r="F118" s="82"/>
-      <c r="G118" s="82"/>
-      <c r="H118" s="82"/>
-      <c r="I118" s="82"/>
-      <c r="J118" s="82"/>
-      <c r="K118" s="82"/>
-      <c r="L118" s="82"/>
-      <c r="M118" s="82"/>
-      <c r="N118" s="82"/>
-      <c r="O118" s="82"/>
-      <c r="P118" s="82"/>
-      <c r="Q118" s="82"/>
-      <c r="R118" s="82"/>
-      <c r="S118" s="82"/>
-      <c r="T118" s="82"/>
-      <c r="U118" s="82"/>
-      <c r="V118" s="82"/>
-      <c r="W118" s="82"/>
-      <c r="X118" s="82"/>
-      <c r="Y118" s="82"/>
+      <c r="D118" s="80"/>
+      <c r="E118" s="80"/>
+      <c r="F118" s="80"/>
+      <c r="G118" s="80"/>
+      <c r="H118" s="80"/>
+      <c r="I118" s="80"/>
+      <c r="J118" s="80"/>
+      <c r="K118" s="80"/>
+      <c r="L118" s="80"/>
+      <c r="M118" s="80"/>
+      <c r="N118" s="80"/>
+      <c r="O118" s="80"/>
+      <c r="P118" s="80"/>
+      <c r="Q118" s="80"/>
+      <c r="R118" s="80"/>
+      <c r="S118" s="80"/>
+      <c r="T118" s="80"/>
+      <c r="U118" s="80"/>
+      <c r="V118" s="80"/>
+      <c r="W118" s="80"/>
+      <c r="X118" s="80"/>
+      <c r="Y118" s="80"/>
     </row>
     <row r="119" spans="3:27">
-      <c r="D119" s="82"/>
-      <c r="E119" s="82"/>
-      <c r="F119" s="82"/>
-      <c r="G119" s="82"/>
-      <c r="H119" s="82"/>
-      <c r="I119" s="82"/>
-      <c r="J119" s="82"/>
-      <c r="K119" s="82"/>
-      <c r="L119" s="82"/>
-      <c r="M119" s="82"/>
-      <c r="N119" s="82"/>
-      <c r="O119" s="82"/>
-      <c r="P119" s="82"/>
-      <c r="Q119" s="82"/>
-      <c r="R119" s="82"/>
-      <c r="S119" s="82"/>
-      <c r="T119" s="82"/>
-      <c r="U119" s="82"/>
-      <c r="V119" s="82"/>
-      <c r="W119" s="82"/>
-      <c r="X119" s="82"/>
-      <c r="Y119" s="82"/>
+      <c r="D119" s="80"/>
+      <c r="E119" s="80"/>
+      <c r="F119" s="80"/>
+      <c r="G119" s="80"/>
+      <c r="H119" s="80"/>
+      <c r="I119" s="80"/>
+      <c r="J119" s="80"/>
+      <c r="K119" s="80"/>
+      <c r="L119" s="80"/>
+      <c r="M119" s="80"/>
+      <c r="N119" s="80"/>
+      <c r="O119" s="80"/>
+      <c r="P119" s="80"/>
+      <c r="Q119" s="80"/>
+      <c r="R119" s="80"/>
+      <c r="S119" s="80"/>
+      <c r="T119" s="80"/>
+      <c r="U119" s="80"/>
+      <c r="V119" s="80"/>
+      <c r="W119" s="80"/>
+      <c r="X119" s="80"/>
+      <c r="Y119" s="80"/>
     </row>
     <row r="120" spans="3:27">
-      <c r="D120" s="82"/>
-      <c r="E120" s="82"/>
-      <c r="F120" s="82"/>
-      <c r="G120" s="82"/>
-      <c r="H120" s="82"/>
-      <c r="I120" s="82"/>
-      <c r="J120" s="82"/>
-      <c r="K120" s="82"/>
-      <c r="L120" s="82"/>
-      <c r="M120" s="82"/>
-      <c r="N120" s="82"/>
-      <c r="O120" s="82"/>
-      <c r="P120" s="82"/>
-      <c r="Q120" s="82"/>
-      <c r="R120" s="82"/>
-      <c r="S120" s="82"/>
-      <c r="T120" s="82"/>
-      <c r="U120" s="82"/>
-      <c r="V120" s="82"/>
-      <c r="W120" s="82"/>
-      <c r="X120" s="82"/>
-      <c r="Y120" s="82"/>
+      <c r="D120" s="80"/>
+      <c r="E120" s="80"/>
+      <c r="F120" s="80"/>
+      <c r="G120" s="80"/>
+      <c r="H120" s="80"/>
+      <c r="I120" s="80"/>
+      <c r="J120" s="80"/>
+      <c r="K120" s="80"/>
+      <c r="L120" s="80"/>
+      <c r="M120" s="80"/>
+      <c r="N120" s="80"/>
+      <c r="O120" s="80"/>
+      <c r="P120" s="80"/>
+      <c r="Q120" s="80"/>
+      <c r="R120" s="80"/>
+      <c r="S120" s="80"/>
+      <c r="T120" s="80"/>
+      <c r="U120" s="80"/>
+      <c r="V120" s="80"/>
+      <c r="W120" s="80"/>
+      <c r="X120" s="80"/>
+      <c r="Y120" s="80"/>
     </row>
     <row r="121" spans="3:27">
       <c r="C121" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D121" s="82" t="s">
+      <c r="D121" s="80" t="s">
         <v>139</v>
       </c>
-      <c r="E121" s="82"/>
-      <c r="F121" s="82"/>
-      <c r="G121" s="82"/>
-      <c r="H121" s="82"/>
-      <c r="I121" s="82"/>
-      <c r="J121" s="82"/>
-      <c r="K121" s="82"/>
-      <c r="L121" s="82"/>
-      <c r="M121" s="82"/>
-      <c r="N121" s="82"/>
-      <c r="O121" s="82"/>
-      <c r="P121" s="82"/>
-      <c r="Q121" s="82"/>
-      <c r="R121" s="82"/>
-      <c r="S121" s="82"/>
-      <c r="T121" s="82"/>
-      <c r="U121" s="82"/>
-      <c r="V121" s="82"/>
-      <c r="W121" s="82"/>
-      <c r="X121" s="82"/>
-      <c r="Y121" s="82"/>
+      <c r="E121" s="80"/>
+      <c r="F121" s="80"/>
+      <c r="G121" s="80"/>
+      <c r="H121" s="80"/>
+      <c r="I121" s="80"/>
+      <c r="J121" s="80"/>
+      <c r="K121" s="80"/>
+      <c r="L121" s="80"/>
+      <c r="M121" s="80"/>
+      <c r="N121" s="80"/>
+      <c r="O121" s="80"/>
+      <c r="P121" s="80"/>
+      <c r="Q121" s="80"/>
+      <c r="R121" s="80"/>
+      <c r="S121" s="80"/>
+      <c r="T121" s="80"/>
+      <c r="U121" s="80"/>
+      <c r="V121" s="80"/>
+      <c r="W121" s="80"/>
+      <c r="X121" s="80"/>
+      <c r="Y121" s="80"/>
     </row>
     <row r="122" spans="3:27">
-      <c r="D122" s="82"/>
-      <c r="E122" s="82"/>
-      <c r="F122" s="82"/>
-      <c r="G122" s="82"/>
-      <c r="H122" s="82"/>
-      <c r="I122" s="82"/>
-      <c r="J122" s="82"/>
-      <c r="K122" s="82"/>
-      <c r="L122" s="82"/>
-      <c r="M122" s="82"/>
-      <c r="N122" s="82"/>
-      <c r="O122" s="82"/>
-      <c r="P122" s="82"/>
-      <c r="Q122" s="82"/>
-      <c r="R122" s="82"/>
-      <c r="S122" s="82"/>
-      <c r="T122" s="82"/>
-      <c r="U122" s="82"/>
-      <c r="V122" s="82"/>
-      <c r="W122" s="82"/>
-      <c r="X122" s="82"/>
-      <c r="Y122" s="82"/>
+      <c r="D122" s="80"/>
+      <c r="E122" s="80"/>
+      <c r="F122" s="80"/>
+      <c r="G122" s="80"/>
+      <c r="H122" s="80"/>
+      <c r="I122" s="80"/>
+      <c r="J122" s="80"/>
+      <c r="K122" s="80"/>
+      <c r="L122" s="80"/>
+      <c r="M122" s="80"/>
+      <c r="N122" s="80"/>
+      <c r="O122" s="80"/>
+      <c r="P122" s="80"/>
+      <c r="Q122" s="80"/>
+      <c r="R122" s="80"/>
+      <c r="S122" s="80"/>
+      <c r="T122" s="80"/>
+      <c r="U122" s="80"/>
+      <c r="V122" s="80"/>
+      <c r="W122" s="80"/>
+      <c r="X122" s="80"/>
+      <c r="Y122" s="80"/>
     </row>
     <row r="123" spans="3:27" ht="14.25" customHeight="1">
       <c r="D123" s="81" t="s">
@@ -12050,84 +12061,84 @@
       <c r="C125" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D125" s="83" t="s">
+      <c r="D125" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="E125" s="83"/>
-      <c r="F125" s="83"/>
-      <c r="G125" s="83"/>
-      <c r="H125" s="83"/>
-      <c r="I125" s="83"/>
-      <c r="J125" s="83"/>
-      <c r="K125" s="83"/>
-      <c r="L125" s="83"/>
-      <c r="M125" s="83"/>
-      <c r="N125" s="83"/>
-      <c r="O125" s="83"/>
-      <c r="P125" s="83"/>
-      <c r="Q125" s="83"/>
-      <c r="R125" s="83"/>
-      <c r="S125" s="83"/>
-      <c r="T125" s="83"/>
-      <c r="U125" s="83"/>
-      <c r="V125" s="83"/>
-      <c r="W125" s="83"/>
-      <c r="X125" s="83"/>
-      <c r="Y125" s="83"/>
-      <c r="Z125" s="83"/>
-      <c r="AA125" s="83"/>
+      <c r="E125" s="82"/>
+      <c r="F125" s="82"/>
+      <c r="G125" s="82"/>
+      <c r="H125" s="82"/>
+      <c r="I125" s="82"/>
+      <c r="J125" s="82"/>
+      <c r="K125" s="82"/>
+      <c r="L125" s="82"/>
+      <c r="M125" s="82"/>
+      <c r="N125" s="82"/>
+      <c r="O125" s="82"/>
+      <c r="P125" s="82"/>
+      <c r="Q125" s="82"/>
+      <c r="R125" s="82"/>
+      <c r="S125" s="82"/>
+      <c r="T125" s="82"/>
+      <c r="U125" s="82"/>
+      <c r="V125" s="82"/>
+      <c r="W125" s="82"/>
+      <c r="X125" s="82"/>
+      <c r="Y125" s="82"/>
+      <c r="Z125" s="82"/>
+      <c r="AA125" s="82"/>
     </row>
     <row r="126" spans="3:27">
-      <c r="D126" s="83"/>
-      <c r="E126" s="83"/>
-      <c r="F126" s="83"/>
-      <c r="G126" s="83"/>
-      <c r="H126" s="83"/>
-      <c r="I126" s="83"/>
-      <c r="J126" s="83"/>
-      <c r="K126" s="83"/>
-      <c r="L126" s="83"/>
-      <c r="M126" s="83"/>
-      <c r="N126" s="83"/>
-      <c r="O126" s="83"/>
-      <c r="P126" s="83"/>
-      <c r="Q126" s="83"/>
-      <c r="R126" s="83"/>
-      <c r="S126" s="83"/>
-      <c r="T126" s="83"/>
-      <c r="U126" s="83"/>
-      <c r="V126" s="83"/>
-      <c r="W126" s="83"/>
-      <c r="X126" s="83"/>
-      <c r="Y126" s="83"/>
-      <c r="Z126" s="83"/>
-      <c r="AA126" s="83"/>
+      <c r="D126" s="82"/>
+      <c r="E126" s="82"/>
+      <c r="F126" s="82"/>
+      <c r="G126" s="82"/>
+      <c r="H126" s="82"/>
+      <c r="I126" s="82"/>
+      <c r="J126" s="82"/>
+      <c r="K126" s="82"/>
+      <c r="L126" s="82"/>
+      <c r="M126" s="82"/>
+      <c r="N126" s="82"/>
+      <c r="O126" s="82"/>
+      <c r="P126" s="82"/>
+      <c r="Q126" s="82"/>
+      <c r="R126" s="82"/>
+      <c r="S126" s="82"/>
+      <c r="T126" s="82"/>
+      <c r="U126" s="82"/>
+      <c r="V126" s="82"/>
+      <c r="W126" s="82"/>
+      <c r="X126" s="82"/>
+      <c r="Y126" s="82"/>
+      <c r="Z126" s="82"/>
+      <c r="AA126" s="82"/>
     </row>
     <row r="127" spans="3:27">
-      <c r="D127" s="83"/>
-      <c r="E127" s="83"/>
-      <c r="F127" s="83"/>
-      <c r="G127" s="83"/>
-      <c r="H127" s="83"/>
-      <c r="I127" s="83"/>
-      <c r="J127" s="83"/>
-      <c r="K127" s="83"/>
-      <c r="L127" s="83"/>
-      <c r="M127" s="83"/>
-      <c r="N127" s="83"/>
-      <c r="O127" s="83"/>
-      <c r="P127" s="83"/>
-      <c r="Q127" s="83"/>
-      <c r="R127" s="83"/>
-      <c r="S127" s="83"/>
-      <c r="T127" s="83"/>
-      <c r="U127" s="83"/>
-      <c r="V127" s="83"/>
-      <c r="W127" s="83"/>
-      <c r="X127" s="83"/>
-      <c r="Y127" s="83"/>
-      <c r="Z127" s="83"/>
-      <c r="AA127" s="83"/>
+      <c r="D127" s="82"/>
+      <c r="E127" s="82"/>
+      <c r="F127" s="82"/>
+      <c r="G127" s="82"/>
+      <c r="H127" s="82"/>
+      <c r="I127" s="82"/>
+      <c r="J127" s="82"/>
+      <c r="K127" s="82"/>
+      <c r="L127" s="82"/>
+      <c r="M127" s="82"/>
+      <c r="N127" s="82"/>
+      <c r="O127" s="82"/>
+      <c r="P127" s="82"/>
+      <c r="Q127" s="82"/>
+      <c r="R127" s="82"/>
+      <c r="S127" s="82"/>
+      <c r="T127" s="82"/>
+      <c r="U127" s="82"/>
+      <c r="V127" s="82"/>
+      <c r="W127" s="82"/>
+      <c r="X127" s="82"/>
+      <c r="Y127" s="82"/>
+      <c r="Z127" s="82"/>
+      <c r="AA127" s="82"/>
     </row>
     <row r="128" spans="3:27">
       <c r="C128" s="29" t="s">
@@ -12199,78 +12210,78 @@
       <c r="C132" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D132" s="82" t="s">
+      <c r="D132" s="80" t="s">
         <v>145</v>
       </c>
-      <c r="E132" s="82"/>
-      <c r="F132" s="82"/>
-      <c r="G132" s="82"/>
-      <c r="H132" s="82"/>
-      <c r="I132" s="82"/>
-      <c r="J132" s="82"/>
-      <c r="K132" s="82"/>
-      <c r="L132" s="82"/>
-      <c r="M132" s="82"/>
-      <c r="N132" s="82"/>
-      <c r="O132" s="82"/>
-      <c r="P132" s="82"/>
-      <c r="Q132" s="82"/>
-      <c r="R132" s="82"/>
-      <c r="S132" s="82"/>
-      <c r="T132" s="82"/>
-      <c r="U132" s="82"/>
-      <c r="V132" s="82"/>
-      <c r="W132" s="82"/>
-      <c r="X132" s="82"/>
-      <c r="Y132" s="82"/>
+      <c r="E132" s="80"/>
+      <c r="F132" s="80"/>
+      <c r="G132" s="80"/>
+      <c r="H132" s="80"/>
+      <c r="I132" s="80"/>
+      <c r="J132" s="80"/>
+      <c r="K132" s="80"/>
+      <c r="L132" s="80"/>
+      <c r="M132" s="80"/>
+      <c r="N132" s="80"/>
+      <c r="O132" s="80"/>
+      <c r="P132" s="80"/>
+      <c r="Q132" s="80"/>
+      <c r="R132" s="80"/>
+      <c r="S132" s="80"/>
+      <c r="T132" s="80"/>
+      <c r="U132" s="80"/>
+      <c r="V132" s="80"/>
+      <c r="W132" s="80"/>
+      <c r="X132" s="80"/>
+      <c r="Y132" s="80"/>
     </row>
     <row r="133" spans="2:25">
-      <c r="D133" s="82"/>
-      <c r="E133" s="82"/>
-      <c r="F133" s="82"/>
-      <c r="G133" s="82"/>
-      <c r="H133" s="82"/>
-      <c r="I133" s="82"/>
-      <c r="J133" s="82"/>
-      <c r="K133" s="82"/>
-      <c r="L133" s="82"/>
-      <c r="M133" s="82"/>
-      <c r="N133" s="82"/>
-      <c r="O133" s="82"/>
-      <c r="P133" s="82"/>
-      <c r="Q133" s="82"/>
-      <c r="R133" s="82"/>
-      <c r="S133" s="82"/>
-      <c r="T133" s="82"/>
-      <c r="U133" s="82"/>
-      <c r="V133" s="82"/>
-      <c r="W133" s="82"/>
-      <c r="X133" s="82"/>
-      <c r="Y133" s="82"/>
+      <c r="D133" s="80"/>
+      <c r="E133" s="80"/>
+      <c r="F133" s="80"/>
+      <c r="G133" s="80"/>
+      <c r="H133" s="80"/>
+      <c r="I133" s="80"/>
+      <c r="J133" s="80"/>
+      <c r="K133" s="80"/>
+      <c r="L133" s="80"/>
+      <c r="M133" s="80"/>
+      <c r="N133" s="80"/>
+      <c r="O133" s="80"/>
+      <c r="P133" s="80"/>
+      <c r="Q133" s="80"/>
+      <c r="R133" s="80"/>
+      <c r="S133" s="80"/>
+      <c r="T133" s="80"/>
+      <c r="U133" s="80"/>
+      <c r="V133" s="80"/>
+      <c r="W133" s="80"/>
+      <c r="X133" s="80"/>
+      <c r="Y133" s="80"/>
     </row>
     <row r="134" spans="2:25">
-      <c r="D134" s="82"/>
-      <c r="E134" s="82"/>
-      <c r="F134" s="82"/>
-      <c r="G134" s="82"/>
-      <c r="H134" s="82"/>
-      <c r="I134" s="82"/>
-      <c r="J134" s="82"/>
-      <c r="K134" s="82"/>
-      <c r="L134" s="82"/>
-      <c r="M134" s="82"/>
-      <c r="N134" s="82"/>
-      <c r="O134" s="82"/>
-      <c r="P134" s="82"/>
-      <c r="Q134" s="82"/>
-      <c r="R134" s="82"/>
-      <c r="S134" s="82"/>
-      <c r="T134" s="82"/>
-      <c r="U134" s="82"/>
-      <c r="V134" s="82"/>
-      <c r="W134" s="82"/>
-      <c r="X134" s="82"/>
-      <c r="Y134" s="82"/>
+      <c r="D134" s="80"/>
+      <c r="E134" s="80"/>
+      <c r="F134" s="80"/>
+      <c r="G134" s="80"/>
+      <c r="H134" s="80"/>
+      <c r="I134" s="80"/>
+      <c r="J134" s="80"/>
+      <c r="K134" s="80"/>
+      <c r="L134" s="80"/>
+      <c r="M134" s="80"/>
+      <c r="N134" s="80"/>
+      <c r="O134" s="80"/>
+      <c r="P134" s="80"/>
+      <c r="Q134" s="80"/>
+      <c r="R134" s="80"/>
+      <c r="S134" s="80"/>
+      <c r="T134" s="80"/>
+      <c r="U134" s="80"/>
+      <c r="V134" s="80"/>
+      <c r="W134" s="80"/>
+      <c r="X134" s="80"/>
+      <c r="Y134" s="80"/>
     </row>
     <row r="135" spans="2:25">
       <c r="C135" s="29" t="s">
@@ -12516,78 +12527,78 @@
     </row>
     <row r="149" spans="2:26">
       <c r="C149" s="29"/>
-      <c r="D149" s="82" t="s">
+      <c r="D149" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="E149" s="82"/>
-      <c r="F149" s="82"/>
-      <c r="G149" s="82"/>
-      <c r="H149" s="82"/>
-      <c r="I149" s="82"/>
-      <c r="J149" s="82"/>
-      <c r="K149" s="82"/>
-      <c r="L149" s="82"/>
-      <c r="M149" s="82"/>
-      <c r="N149" s="82"/>
-      <c r="O149" s="82"/>
-      <c r="P149" s="82"/>
-      <c r="Q149" s="82"/>
-      <c r="R149" s="82"/>
-      <c r="S149" s="82"/>
-      <c r="T149" s="82"/>
-      <c r="U149" s="82"/>
-      <c r="V149" s="82"/>
-      <c r="W149" s="82"/>
-      <c r="X149" s="82"/>
-      <c r="Y149" s="82"/>
+      <c r="E149" s="80"/>
+      <c r="F149" s="80"/>
+      <c r="G149" s="80"/>
+      <c r="H149" s="80"/>
+      <c r="I149" s="80"/>
+      <c r="J149" s="80"/>
+      <c r="K149" s="80"/>
+      <c r="L149" s="80"/>
+      <c r="M149" s="80"/>
+      <c r="N149" s="80"/>
+      <c r="O149" s="80"/>
+      <c r="P149" s="80"/>
+      <c r="Q149" s="80"/>
+      <c r="R149" s="80"/>
+      <c r="S149" s="80"/>
+      <c r="T149" s="80"/>
+      <c r="U149" s="80"/>
+      <c r="V149" s="80"/>
+      <c r="W149" s="80"/>
+      <c r="X149" s="80"/>
+      <c r="Y149" s="80"/>
     </row>
     <row r="150" spans="2:26">
-      <c r="D150" s="82"/>
-      <c r="E150" s="82"/>
-      <c r="F150" s="82"/>
-      <c r="G150" s="82"/>
-      <c r="H150" s="82"/>
-      <c r="I150" s="82"/>
-      <c r="J150" s="82"/>
-      <c r="K150" s="82"/>
-      <c r="L150" s="82"/>
-      <c r="M150" s="82"/>
-      <c r="N150" s="82"/>
-      <c r="O150" s="82"/>
-      <c r="P150" s="82"/>
-      <c r="Q150" s="82"/>
-      <c r="R150" s="82"/>
-      <c r="S150" s="82"/>
-      <c r="T150" s="82"/>
-      <c r="U150" s="82"/>
-      <c r="V150" s="82"/>
-      <c r="W150" s="82"/>
-      <c r="X150" s="82"/>
-      <c r="Y150" s="82"/>
+      <c r="D150" s="80"/>
+      <c r="E150" s="80"/>
+      <c r="F150" s="80"/>
+      <c r="G150" s="80"/>
+      <c r="H150" s="80"/>
+      <c r="I150" s="80"/>
+      <c r="J150" s="80"/>
+      <c r="K150" s="80"/>
+      <c r="L150" s="80"/>
+      <c r="M150" s="80"/>
+      <c r="N150" s="80"/>
+      <c r="O150" s="80"/>
+      <c r="P150" s="80"/>
+      <c r="Q150" s="80"/>
+      <c r="R150" s="80"/>
+      <c r="S150" s="80"/>
+      <c r="T150" s="80"/>
+      <c r="U150" s="80"/>
+      <c r="V150" s="80"/>
+      <c r="W150" s="80"/>
+      <c r="X150" s="80"/>
+      <c r="Y150" s="80"/>
     </row>
     <row r="151" spans="2:26">
-      <c r="D151" s="82"/>
-      <c r="E151" s="82"/>
-      <c r="F151" s="82"/>
-      <c r="G151" s="82"/>
-      <c r="H151" s="82"/>
-      <c r="I151" s="82"/>
-      <c r="J151" s="82"/>
-      <c r="K151" s="82"/>
-      <c r="L151" s="82"/>
-      <c r="M151" s="82"/>
-      <c r="N151" s="82"/>
-      <c r="O151" s="82"/>
-      <c r="P151" s="82"/>
-      <c r="Q151" s="82"/>
-      <c r="R151" s="82"/>
-      <c r="S151" s="82"/>
-      <c r="T151" s="82"/>
-      <c r="U151" s="82"/>
-      <c r="V151" s="82"/>
-      <c r="W151" s="82"/>
-      <c r="X151" s="82"/>
-      <c r="Y151" s="82"/>
+      <c r="D151" s="80"/>
+      <c r="E151" s="80"/>
+      <c r="F151" s="80"/>
+      <c r="G151" s="80"/>
+      <c r="H151" s="80"/>
+      <c r="I151" s="80"/>
+      <c r="J151" s="80"/>
+      <c r="K151" s="80"/>
+      <c r="L151" s="80"/>
+      <c r="M151" s="80"/>
+      <c r="N151" s="80"/>
+      <c r="O151" s="80"/>
+      <c r="P151" s="80"/>
+      <c r="Q151" s="80"/>
+      <c r="R151" s="80"/>
+      <c r="S151" s="80"/>
+      <c r="T151" s="80"/>
+      <c r="U151" s="80"/>
+      <c r="V151" s="80"/>
+      <c r="W151" s="80"/>
+      <c r="X151" s="80"/>
+      <c r="Y151" s="80"/>
     </row>
     <row r="152" spans="2:26">
       <c r="B152" s="1" t="s">
@@ -12672,17 +12683,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D94:Y95"/>
-    <mergeCell ref="D96:Y97"/>
-    <mergeCell ref="D101:Y102"/>
-    <mergeCell ref="D103:Y104"/>
-    <mergeCell ref="D86:Y89"/>
-    <mergeCell ref="D90:Y92"/>
-    <mergeCell ref="Z108:AV109"/>
-    <mergeCell ref="D108:Y109"/>
-    <mergeCell ref="D117:Y120"/>
-    <mergeCell ref="D121:Y122"/>
-    <mergeCell ref="D123:Z124"/>
     <mergeCell ref="D136:Y139"/>
     <mergeCell ref="D142:Y145"/>
     <mergeCell ref="D149:Y151"/>
@@ -12690,6 +12690,17 @@
     <mergeCell ref="D125:AA127"/>
     <mergeCell ref="D128:Y129"/>
     <mergeCell ref="D132:Y134"/>
+    <mergeCell ref="Z108:AV109"/>
+    <mergeCell ref="D108:Y109"/>
+    <mergeCell ref="D117:Y120"/>
+    <mergeCell ref="D121:Y122"/>
+    <mergeCell ref="D123:Z124"/>
+    <mergeCell ref="D94:Y95"/>
+    <mergeCell ref="D96:Y97"/>
+    <mergeCell ref="D101:Y102"/>
+    <mergeCell ref="D103:Y104"/>
+    <mergeCell ref="D86:Y89"/>
+    <mergeCell ref="D90:Y92"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="R11" r:id="rId1" xr:uid="{3A32E811-E794-46FB-A010-EBB0450F323B}"/>
@@ -12707,6 +12718,7 @@
     <hyperlink ref="K18" r:id="rId13" xr:uid="{F6F6BDA3-2ACF-44F4-B3B7-59842082DB68}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId14"/>
 </worksheet>
 </file>
 
@@ -13449,7 +13461,9 @@
       <c r="AY4" s="48">
         <v>35.261000000000003</v>
       </c>
-      <c r="AZ4" s="48"/>
+      <c r="AZ4" s="48">
+        <v>35.65</v>
+      </c>
       <c r="BS4" s="48">
         <f>SUM(AI4:AL4)</f>
         <v>78.716999999999999</v>
@@ -13548,7 +13562,9 @@
       <c r="AY5" s="48">
         <v>40.450000000000003</v>
       </c>
-      <c r="AZ5" s="48"/>
+      <c r="AZ5" s="48">
+        <v>43.78</v>
+      </c>
       <c r="BS5" s="48">
         <f>SUM(AI5:AL5)</f>
         <v>237.50200000000001</v>
@@ -13664,7 +13680,7 @@
       </c>
       <c r="AZ6" s="50">
         <f>SUM(AZ4:AZ5)</f>
-        <v>0</v>
+        <v>79.430000000000007</v>
       </c>
       <c r="BA6" s="35"/>
       <c r="BB6" s="35"/>
@@ -13825,7 +13841,7 @@
       </c>
       <c r="AZ8" s="49">
         <f t="shared" si="9"/>
-        <v>-1</v>
+        <v>0.12980921594726502</v>
       </c>
       <c r="BT8" s="49">
         <f t="shared" ref="BT8" si="10">BT4/BS4-1</f>
@@ -13912,7 +13928,7 @@
       </c>
       <c r="AZ9" s="49">
         <f t="shared" si="9"/>
-        <v>-1</v>
+        <v>6.0305158634051947E-2</v>
       </c>
       <c r="BT9" s="49">
         <f t="shared" ref="BT9:BU9" si="12">BT5/BS5-1</f>
@@ -13945,61 +13961,61 @@
       <c r="B10" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="AM10" s="79">
+      <c r="AM10" s="78">
         <f t="shared" ref="AM10:AX10" si="13">AM6/AI6-1</f>
         <v>5.9321042990217121E-2</v>
       </c>
-      <c r="AN10" s="79">
+      <c r="AN10" s="78">
         <f t="shared" si="13"/>
         <v>9.132600919775169E-2</v>
       </c>
-      <c r="AO10" s="79">
+      <c r="AO10" s="78">
         <f t="shared" si="13"/>
         <v>9.098283087738257E-2</v>
       </c>
-      <c r="AP10" s="79">
+      <c r="AP10" s="78">
         <f t="shared" si="13"/>
         <v>4.6989585967493142E-2</v>
       </c>
-      <c r="AQ10" s="79">
+      <c r="AQ10" s="78">
         <f t="shared" si="13"/>
         <v>-3.5051571679115101E-2</v>
       </c>
-      <c r="AR10" s="79">
+      <c r="AR10" s="78">
         <f t="shared" si="13"/>
         <v>-7.4436081424340772E-2</v>
       </c>
-      <c r="AS10" s="79">
+      <c r="AS10" s="78">
         <f t="shared" si="13"/>
         <v>-6.837670384138772E-2</v>
       </c>
-      <c r="AT10" s="79">
+      <c r="AT10" s="78">
         <f t="shared" si="13"/>
         <v>-0.22070351096765672</v>
       </c>
-      <c r="AU10" s="79">
+      <c r="AU10" s="78">
         <f t="shared" si="13"/>
         <v>-0.14219804522172375</v>
       </c>
-      <c r="AV10" s="79">
+      <c r="AV10" s="78">
         <f t="shared" si="13"/>
         <v>-7.8740356646009868E-2</v>
       </c>
-      <c r="AW10" s="79">
+      <c r="AW10" s="78">
         <f>AW6/AS6-1</f>
         <v>-4.2323960522465565E-2</v>
       </c>
-      <c r="AX10" s="79">
+      <c r="AX10" s="78">
         <f t="shared" si="13"/>
         <v>0.12932674020540125</v>
       </c>
-      <c r="AY10" s="79">
+      <c r="AY10" s="78">
         <f t="shared" si="9"/>
         <v>0.121794016980042</v>
       </c>
-      <c r="AZ10" s="79">
+      <c r="AZ10" s="78">
         <f t="shared" si="9"/>
-        <v>-1</v>
+        <v>9.0412388117072195E-2</v>
       </c>
       <c r="BA10" s="35"/>
       <c r="BB10" s="35"/>
@@ -14007,35 +14023,35 @@
       <c r="BD10" s="35"/>
       <c r="BE10" s="35"/>
       <c r="BF10" s="35"/>
-      <c r="BT10" s="79">
+      <c r="BT10" s="78">
         <f t="shared" ref="BT10:BU10" si="14">BT6/BS6-1</f>
         <v>7.1257577817904538E-2</v>
       </c>
-      <c r="BU10" s="79">
+      <c r="BU10" s="78">
         <f t="shared" si="14"/>
         <v>-0.10284219724164001</v>
       </c>
-      <c r="BV10" s="79">
+      <c r="BV10" s="78">
         <f>BV6/BU6-1</f>
         <v>-3.7563258026941826E-2</v>
       </c>
-      <c r="BW10" s="80">
+      <c r="BW10" s="79">
         <f t="shared" ref="BW10:CA10" si="15">BW6/BV6-1</f>
         <v>3.2270887322306541E-2</v>
       </c>
-      <c r="BX10" s="80">
+      <c r="BX10" s="79">
         <f t="shared" si="15"/>
         <v>7.8255487391631684E-2</v>
       </c>
-      <c r="BY10" s="80">
+      <c r="BY10" s="79">
         <f t="shared" si="15"/>
         <v>6.470361122859658E-2</v>
       </c>
-      <c r="BZ10" s="80">
+      <c r="BZ10" s="79">
         <f t="shared" si="15"/>
         <v>5.660546647952347E-2</v>
       </c>
-      <c r="CA10" s="80">
+      <c r="CA10" s="79">
         <f t="shared" si="15"/>
         <v>5.8519541828879307E-2</v>
       </c>
@@ -14167,9 +14183,9 @@
         <f t="shared" si="17"/>
         <v>0.46573153174571724</v>
       </c>
-      <c r="AZ12" s="49" t="e">
+      <c r="AZ12" s="49">
         <f t="shared" ref="AZ12" si="18">AZ4/AZ6</f>
-        <v>#DIV/0!</v>
+        <v>0.44882286289814927</v>
       </c>
       <c r="BS12" s="49">
         <f t="shared" ref="BS12:BU12" si="19">BS4/BS6</f>
@@ -14280,9 +14296,9 @@
         <f t="shared" si="23"/>
         <v>0.53426846825428265</v>
       </c>
-      <c r="AZ13" s="49" t="e">
+      <c r="AZ13" s="49">
         <f t="shared" ref="AZ13" si="24">AZ5/AZ6</f>
-        <v>#DIV/0!</v>
+        <v>0.55117713710185068</v>
       </c>
       <c r="BS13" s="49">
         <f t="shared" ref="BS13:BU13" si="25">BS5/BS6</f>
@@ -14382,7 +14398,9 @@
       <c r="AY15" s="48">
         <v>66.456000000000003</v>
       </c>
-      <c r="AZ15" s="48"/>
+      <c r="AZ15" s="48">
+        <v>67.59</v>
+      </c>
       <c r="BS15" s="48">
         <f>SUM(AI15:AL15)</f>
         <v>265.96300000000002</v>
@@ -14461,7 +14479,9 @@
       <c r="AY16" s="48">
         <v>9.2550000000000008</v>
       </c>
-      <c r="AZ16" s="48"/>
+      <c r="AZ16" s="48">
+        <v>11.84</v>
+      </c>
       <c r="BS16" s="48">
         <f>SUM(AI16:AL16)</f>
         <v>50.256</v>
@@ -14479,7 +14499,7 @@
         <v>41.515000000000001</v>
       </c>
     </row>
-    <row r="17" spans="2:134">
+    <row r="17" spans="2:134" ht="15">
       <c r="B17" s="1" t="s">
         <v>217</v>
       </c>
@@ -14487,77 +14507,77 @@
       <c r="AF17" s="48"/>
       <c r="AG17" s="48"/>
       <c r="AH17" s="48"/>
-      <c r="AI17" s="48">
+      <c r="AI17" s="50">
         <f t="shared" ref="AI17:AV17" si="28">SUM(AI15:AI16)</f>
         <v>76.971000000000004</v>
       </c>
-      <c r="AJ17" s="48">
+      <c r="AJ17" s="50">
         <f t="shared" si="28"/>
         <v>78.28</v>
       </c>
-      <c r="AK17" s="48">
+      <c r="AK17" s="50">
         <f t="shared" si="28"/>
         <v>73.97</v>
       </c>
-      <c r="AL17" s="48">
+      <c r="AL17" s="50">
         <f t="shared" si="28"/>
         <v>86.998000000000047</v>
       </c>
-      <c r="AM17" s="48">
+      <c r="AM17" s="50">
         <f t="shared" si="28"/>
         <v>81.536999999999992</v>
       </c>
-      <c r="AN17" s="48">
+      <c r="AN17" s="50">
         <f t="shared" si="28"/>
         <v>85.429000000000002</v>
       </c>
-      <c r="AO17" s="48">
+      <c r="AO17" s="50">
         <f t="shared" si="28"/>
         <v>80.699999999999989</v>
       </c>
-      <c r="AP17" s="48">
+      <c r="AP17" s="50">
         <f t="shared" si="28"/>
         <v>91.086000000000041</v>
       </c>
-      <c r="AQ17" s="48">
+      <c r="AQ17" s="50">
         <f t="shared" si="28"/>
         <v>78.679000000000002</v>
       </c>
-      <c r="AR17" s="48">
+      <c r="AR17" s="50">
         <f t="shared" si="28"/>
         <v>79.072999999999993</v>
       </c>
-      <c r="AS17" s="48">
+      <c r="AS17" s="50">
         <f t="shared" si="28"/>
         <v>75.182000000000002</v>
       </c>
-      <c r="AT17" s="48">
+      <c r="AT17" s="50">
         <f t="shared" si="28"/>
         <v>70.97999999999999</v>
       </c>
-      <c r="AU17" s="48">
+      <c r="AU17" s="50">
         <f t="shared" si="28"/>
         <v>67.491</v>
       </c>
-      <c r="AV17" s="48">
+      <c r="AV17" s="50">
         <f t="shared" si="28"/>
         <v>72.844999999999999</v>
       </c>
-      <c r="AW17" s="48">
+      <c r="AW17" s="50">
         <f>SUM(AW15:AW16)</f>
         <v>72</v>
       </c>
-      <c r="AX17" s="48">
+      <c r="AX17" s="50">
         <f t="shared" ref="AX17" si="29">SUM(AX15:AX16)</f>
         <v>80.162000000000006</v>
       </c>
-      <c r="AY17" s="48">
+      <c r="AY17" s="50">
         <f>SUM(AY15:AY16)</f>
         <v>75.710999999999999</v>
       </c>
-      <c r="AZ17" s="48">
+      <c r="AZ17" s="50">
         <f>SUM(AZ15:AZ16)</f>
-        <v>0</v>
+        <v>79.430000000000007</v>
       </c>
       <c r="BS17" s="48">
         <f>SUM(AI17:AL17)</f>
@@ -14634,7 +14654,7 @@
       </c>
       <c r="AZ19" s="49">
         <f t="shared" si="41"/>
-        <v>-1</v>
+        <v>7.8368805641533035E-2</v>
       </c>
       <c r="BT19" s="49">
         <f t="shared" ref="BT19:BV19" si="42">BT15/BS15-1</f>
@@ -14707,7 +14727,7 @@
       </c>
       <c r="AZ20" s="49">
         <f t="shared" si="41"/>
-        <v>-1</v>
+        <v>0.16455198190223275</v>
       </c>
       <c r="BT20" s="49">
         <f t="shared" ref="BT20:BV20" si="43">BT16/BS16-1</f>
@@ -14780,7 +14800,7 @@
       </c>
       <c r="AZ21" s="49">
         <f t="shared" si="41"/>
-        <v>-1</v>
+        <v>9.0397419177706162E-2</v>
       </c>
       <c r="BT21" s="49">
         <f t="shared" ref="BT21:BV21" si="44">BT17/BS17-1</f>
@@ -14867,9 +14887,9 @@
         <f>AY15/AY17</f>
         <v>0.87775884613860611</v>
       </c>
-      <c r="AZ23" s="49" t="e">
+      <c r="AZ23" s="49">
         <f>AZ15/AZ17</f>
-        <v>#DIV/0!</v>
+        <v>0.85093793277099328</v>
       </c>
       <c r="BS23" s="49">
         <f t="shared" ref="BS23:BT23" si="47">BS15/BS17</f>
@@ -14960,9 +14980,9 @@
         <f>AY16/AY17</f>
         <v>0.122241153861394</v>
       </c>
-      <c r="AZ24" s="49" t="e">
+      <c r="AZ24" s="49">
         <f>AZ16/AZ17</f>
-        <v>#DIV/0!</v>
+        <v>0.14906206722900667</v>
       </c>
       <c r="BS24" s="49">
         <f t="shared" ref="BS24:BT24" si="50">BS16/BS17</f>
@@ -15152,7 +15172,7 @@
       </c>
       <c r="AZ26" s="50">
         <f>AZ6</f>
-        <v>0</v>
+        <v>79.430000000000007</v>
       </c>
       <c r="BA26" s="35"/>
       <c r="BB26" s="35"/>
@@ -15440,7 +15460,9 @@
       <c r="AY27" s="48">
         <v>33.85</v>
       </c>
-      <c r="AZ27" s="48"/>
+      <c r="AZ27" s="48">
+        <v>34.65</v>
+      </c>
       <c r="BK27" s="48">
         <f t="shared" si="53"/>
         <v>174.3</v>
@@ -15495,11 +15517,11 @@
       </c>
       <c r="BX27" s="61">
         <f t="shared" si="67"/>
-        <v>149.760088784</v>
+        <v>143.248780576</v>
       </c>
       <c r="BY27" s="61">
         <f t="shared" si="67"/>
-        <v>157.71695400552002</v>
+        <v>149.05118730192007</v>
       </c>
       <c r="BZ27" s="61">
         <f t="shared" si="67"/>
@@ -15712,7 +15734,7 @@
       </c>
       <c r="AZ28" s="48">
         <f>AZ26-AZ27</f>
-        <v>0</v>
+        <v>44.780000000000008</v>
       </c>
       <c r="BK28" s="48">
         <f t="shared" si="53"/>
@@ -15768,11 +15790,11 @@
       </c>
       <c r="BX28" s="61">
         <f t="shared" si="99"/>
-        <v>175.80532161600001</v>
+        <v>182.31662982400002</v>
       </c>
       <c r="BY28" s="61">
         <f t="shared" si="99"/>
-        <v>188.91371413848006</v>
+        <v>197.57948084208002</v>
       </c>
       <c r="BZ28" s="61">
         <f t="shared" si="99"/>
@@ -15939,7 +15961,9 @@
       <c r="AY29" s="48">
         <v>6.4169999999999998</v>
       </c>
-      <c r="AZ29" s="48"/>
+      <c r="AZ29" s="48">
+        <v>7.76</v>
+      </c>
       <c r="BK29" s="48">
         <f t="shared" si="53"/>
         <v>28.1</v>
@@ -15994,19 +16018,19 @@
       </c>
       <c r="BX29" s="61">
         <f t="shared" si="101"/>
-        <v>30.277583167200003</v>
+        <v>29.9520177568</v>
       </c>
       <c r="BY29" s="61">
         <f t="shared" si="101"/>
-        <v>31.890021469248008</v>
+        <v>31.196760132960005</v>
       </c>
       <c r="BZ29" s="61">
         <f t="shared" si="101"/>
-        <v>33.328919151746412</v>
+        <v>32.23016357531521</v>
       </c>
       <c r="CA29" s="61">
         <f t="shared" ref="CA29" si="102">CA26*CA46</f>
-        <v>35.279312230158368</v>
+        <v>33.34088848124857</v>
       </c>
     </row>
     <row r="30" spans="2:134">
@@ -16165,7 +16189,9 @@
       <c r="AY30" s="48">
         <v>28.13</v>
       </c>
-      <c r="AZ30" s="48"/>
+      <c r="AZ30" s="48">
+        <v>26.71</v>
+      </c>
       <c r="BK30" s="48">
         <f t="shared" si="53"/>
         <v>26.9</v>
@@ -16216,11 +16242,11 @@
       </c>
       <c r="BW30" s="61">
         <f t="shared" ref="BW30:BZ30" si="103">BW26*BW47</f>
-        <v>144.9298416</v>
+        <v>141.91046990000001</v>
       </c>
       <c r="BX30" s="61">
         <f t="shared" si="103"/>
-        <v>149.760088784</v>
+        <v>146.50443468</v>
       </c>
       <c r="BY30" s="61">
         <f t="shared" si="103"/>
@@ -16232,7 +16258,7 @@
       </c>
       <c r="CA30" s="61">
         <f t="shared" ref="CA30" si="104">CA26*CA47</f>
-        <v>162.82759490842326</v>
+        <v>158.95074741060364</v>
       </c>
     </row>
     <row r="31" spans="2:134">
@@ -16419,7 +16445,9 @@
       <c r="AY31" s="48">
         <v>12.55</v>
       </c>
-      <c r="AZ31" s="48"/>
+      <c r="AZ31" s="48">
+        <v>10.15</v>
+      </c>
       <c r="BK31" s="48">
         <f t="shared" si="53"/>
         <v>114.7</v>
@@ -16630,7 +16658,9 @@
       <c r="AY32" s="48">
         <v>2.65</v>
       </c>
-      <c r="AZ32" s="48"/>
+      <c r="AZ32" s="48">
+        <v>2.64</v>
+      </c>
       <c r="BK32" s="48">
         <f t="shared" si="53"/>
         <v>0</v>
@@ -16851,7 +16881,9 @@
       <c r="AY33" s="48">
         <v>0</v>
       </c>
-      <c r="AZ33" s="48"/>
+      <c r="AZ33" s="48">
+        <v>0</v>
+      </c>
       <c r="BK33" s="48">
         <f t="shared" si="53"/>
         <v>0</v>
@@ -17072,7 +17104,9 @@
       <c r="AY34" s="48">
         <v>0.04</v>
       </c>
-      <c r="AZ34" s="48"/>
+      <c r="AZ34" s="48">
+        <v>0</v>
+      </c>
       <c r="BK34" s="48">
         <f t="shared" si="53"/>
         <v>0</v>
@@ -17293,7 +17327,9 @@
       <c r="AY35" s="48">
         <v>2.758</v>
       </c>
-      <c r="AZ35" s="48"/>
+      <c r="AZ35" s="48">
+        <v>3.63</v>
+      </c>
       <c r="BK35" s="48">
         <f t="shared" si="53"/>
         <v>0</v>
@@ -17560,7 +17596,7 @@
       </c>
       <c r="AZ36" s="48">
         <f>AZ28-SUM(AZ29:AZ35)</f>
-        <v>0</v>
+        <v>-6.1099999999999923</v>
       </c>
       <c r="BK36" s="48">
         <f t="shared" si="53"/>
@@ -17612,23 +17648,23 @@
       </c>
       <c r="BW36" s="61">
         <f t="shared" ref="BW36:BZ36" si="108">BW28-SUM(BW29:BW35)</f>
-        <v>-11.775549629999972</v>
+        <v>-8.7561779299999785</v>
       </c>
       <c r="BX36" s="61">
         <f t="shared" si="108"/>
-        <v>-4.2323503351999818</v>
+        <v>5.8601773872000251</v>
       </c>
       <c r="BY36" s="61">
         <f t="shared" si="108"/>
-        <v>4.5061986858720218</v>
+        <v>13.865226725759982</v>
       </c>
       <c r="BZ36" s="61">
         <f t="shared" si="108"/>
-        <v>12.452563199553623</v>
+        <v>13.551318775984839</v>
       </c>
       <c r="CA36" s="61">
         <f t="shared" ref="CA36" si="109">CA28-SUM(CA29:CA35)</f>
-        <v>13.181281492586663</v>
+        <v>18.996552739316087</v>
       </c>
     </row>
     <row r="37" spans="2:134">
@@ -17787,7 +17823,9 @@
       <c r="AY37" s="48">
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="AZ37" s="48"/>
+      <c r="AZ37" s="48">
+        <v>-0.1</v>
+      </c>
       <c r="BK37" s="48">
         <f t="shared" si="53"/>
         <v>-5.3999999999999995</v>
@@ -17838,23 +17876,23 @@
       </c>
       <c r="BW37" s="61">
         <f>BV52*$CF$54</f>
-        <v>2.5151849999999998</v>
+        <v>4.7509050000000004</v>
       </c>
       <c r="BX37" s="61">
         <f>BW52*$CF$54</f>
-        <v>2.0484626226480014</v>
+        <v>4.4070523189595026</v>
       </c>
       <c r="BY37" s="61">
         <f>BX52*$CF$54</f>
-        <v>1.9383946819353814</v>
+        <v>5.2884939892332978</v>
       </c>
       <c r="BZ37" s="61">
         <f>BY52*$CF$54</f>
-        <v>2.2632021876728747</v>
+        <v>6.9328409126154709</v>
       </c>
       <c r="CA37" s="61">
         <f>BZ52*$CF$54</f>
-        <v>3.00487676318909</v>
+        <v>8.6914060218818072</v>
       </c>
     </row>
     <row r="38" spans="2:134">
@@ -18013,7 +18051,9 @@
       <c r="AY38" s="48">
         <v>-0.17799999999999999</v>
       </c>
-      <c r="AZ38" s="48"/>
+      <c r="AZ38" s="48">
+        <v>-0.128</v>
+      </c>
       <c r="BK38" s="48">
         <f t="shared" si="53"/>
         <v>0</v>
@@ -18280,7 +18320,7 @@
       </c>
       <c r="AZ39" s="48">
         <f>AZ36+SUM(AZ37:AZ38)</f>
-        <v>0</v>
+        <v>-6.3379999999999921</v>
       </c>
       <c r="BK39" s="48">
         <f t="shared" si="53"/>
@@ -18332,23 +18372,23 @@
       </c>
       <c r="BW39" s="61">
         <f t="shared" ref="BW39:BZ39" si="114">BW36+SUM(BW37:BW38)</f>
-        <v>-9.2603646299999731</v>
+        <v>-4.0052729299999781</v>
       </c>
       <c r="BX39" s="61">
         <f t="shared" si="114"/>
-        <v>-2.1838877125519804</v>
+        <v>10.267229706159528</v>
       </c>
       <c r="BY39" s="61">
         <f t="shared" si="114"/>
-        <v>6.4445933678074034</v>
+        <v>19.15372071499328</v>
       </c>
       <c r="BZ39" s="61">
         <f t="shared" si="114"/>
-        <v>14.715765387226497</v>
+        <v>20.484159688600311</v>
       </c>
       <c r="CA39" s="61">
         <f t="shared" ref="CA39" si="115">CA36+SUM(CA37:CA38)</f>
-        <v>16.186158255775752</v>
+        <v>27.687958761197894</v>
       </c>
     </row>
     <row r="40" spans="2:134">
@@ -18507,7 +18547,9 @@
       <c r="AY40" s="48">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AZ40" s="48"/>
+      <c r="AZ40" s="48">
+        <v>5.0000000000000001E-3</v>
+      </c>
       <c r="BK40" s="48">
         <f t="shared" si="53"/>
         <v>2.8</v>
@@ -18558,23 +18600,23 @@
       </c>
       <c r="BW40" s="61">
         <f t="shared" ref="BW40:BZ40" si="116">BW39*-BW49</f>
-        <v>1.1112437555999968</v>
+        <v>4.0052729299999784E-2</v>
       </c>
       <c r="BX40" s="61">
         <f t="shared" si="116"/>
-        <v>0.26206652550623766</v>
+        <v>-0.10267229706159528</v>
       </c>
       <c r="BY40" s="61">
         <f t="shared" si="116"/>
-        <v>-0.7733512041368884</v>
+        <v>-0.1915372071499328</v>
       </c>
       <c r="BZ40" s="61">
         <f t="shared" si="116"/>
-        <v>-1.7658918464671796</v>
+        <v>-0.20484159688600312</v>
       </c>
       <c r="CA40" s="61">
         <f t="shared" ref="CA40" si="117">CA39*-CA49</f>
-        <v>-1.9423389906930901</v>
+        <v>-0.27687958761197895</v>
       </c>
     </row>
     <row r="41" spans="2:134" s="2" customFormat="1" ht="15">
@@ -18779,7 +18821,7 @@
       </c>
       <c r="AZ41" s="50">
         <f>AZ39-AZ40</f>
-        <v>0</v>
+        <v>-6.342999999999992</v>
       </c>
       <c r="BA41" s="35"/>
       <c r="BB41" s="35"/>
@@ -18837,243 +18879,243 @@
       </c>
       <c r="BW41" s="62">
         <f>BW39-BW40</f>
-        <v>-10.37160838559997</v>
+        <v>-4.0453256592999782</v>
       </c>
       <c r="BX41" s="62">
         <f>BX39-BX40</f>
-        <v>-2.445954238058218</v>
+        <v>10.369902003221123</v>
       </c>
       <c r="BY41" s="62">
         <f t="shared" ref="BY41:BZ41" si="148">BY39-BY40</f>
-        <v>7.2179445719442921</v>
+        <v>19.345257922143212</v>
       </c>
       <c r="BZ41" s="62">
         <f t="shared" si="148"/>
-        <v>16.481657233693678</v>
+        <v>20.689001285486313</v>
       </c>
       <c r="CA41" s="62">
         <f t="shared" ref="CA41" si="149">CA39-CA40</f>
-        <v>18.128497246468843</v>
+        <v>27.964838348809874</v>
       </c>
       <c r="CB41" s="62">
         <f t="shared" ref="CB41:DG41" si="150">CA41*(1+$CF$55)</f>
-        <v>18.355103462049701</v>
+        <v>28.314398828169995</v>
       </c>
       <c r="CC41" s="62">
         <f t="shared" si="150"/>
-        <v>18.584542255325321</v>
+        <v>28.66832881352212</v>
       </c>
       <c r="CD41" s="62">
         <f t="shared" si="150"/>
-        <v>18.816849033516885</v>
+        <v>29.026682923691144</v>
       </c>
       <c r="CE41" s="62">
         <f t="shared" si="150"/>
-        <v>19.052059646435843</v>
+        <v>29.389516460237282</v>
       </c>
       <c r="CF41" s="62">
         <f t="shared" si="150"/>
-        <v>19.290210392016292</v>
+        <v>29.756885415990247</v>
       </c>
       <c r="CG41" s="62">
         <f t="shared" si="150"/>
-        <v>19.531338021916493</v>
+        <v>30.128846483690126</v>
       </c>
       <c r="CH41" s="62">
         <f t="shared" si="150"/>
-        <v>19.775479747190449</v>
+        <v>30.505457064736252</v>
       </c>
       <c r="CI41" s="62">
         <f t="shared" si="150"/>
-        <v>20.022673244030329</v>
+        <v>30.886775278045455</v>
       </c>
       <c r="CJ41" s="62">
         <f t="shared" si="150"/>
-        <v>20.272956659580707</v>
+        <v>31.27285996902102</v>
       </c>
       <c r="CK41" s="62">
         <f t="shared" si="150"/>
-        <v>20.526368617825465</v>
+        <v>31.663770718633781</v>
       </c>
       <c r="CL41" s="62">
         <f t="shared" si="150"/>
-        <v>20.782948225548282</v>
+        <v>32.059567852616702</v>
       </c>
       <c r="CM41" s="62">
         <f t="shared" si="150"/>
-        <v>21.042735078367635</v>
+        <v>32.46031245077441</v>
       </c>
       <c r="CN41" s="62">
         <f t="shared" si="150"/>
-        <v>21.305769266847228</v>
+        <v>32.866066356409085</v>
       </c>
       <c r="CO41" s="62">
         <f t="shared" si="150"/>
-        <v>21.572091382682817</v>
+        <v>33.276892185864199</v>
       </c>
       <c r="CP41" s="62">
         <f t="shared" si="150"/>
-        <v>21.841742524966353</v>
+        <v>33.692853338187497</v>
       </c>
       <c r="CQ41" s="62">
         <f t="shared" si="150"/>
-        <v>22.114764306528432</v>
+        <v>34.114014004914843</v>
       </c>
       <c r="CR41" s="62">
         <f t="shared" si="150"/>
-        <v>22.391198860360035</v>
+        <v>34.540439179976275</v>
       </c>
       <c r="CS41" s="62">
         <f t="shared" si="150"/>
-        <v>22.671088846114536</v>
+        <v>34.97219466972598</v>
       </c>
       <c r="CT41" s="62">
         <f t="shared" si="150"/>
-        <v>22.954477456690967</v>
+        <v>35.409347103097552</v>
       </c>
       <c r="CU41" s="62">
         <f t="shared" si="150"/>
-        <v>23.241408424899603</v>
+        <v>35.851963941886268</v>
       </c>
       <c r="CV41" s="62">
         <f t="shared" si="150"/>
-        <v>23.531926030210848</v>
+        <v>36.300113491159848</v>
       </c>
       <c r="CW41" s="62">
         <f t="shared" si="150"/>
-        <v>23.826075105588483</v>
+        <v>36.753864909799347</v>
       </c>
       <c r="CX41" s="62">
         <f t="shared" si="150"/>
-        <v>24.123901044408338</v>
+        <v>37.213288221171837</v>
       </c>
       <c r="CY41" s="62">
         <f t="shared" si="150"/>
-        <v>24.425449807463441</v>
+        <v>37.678454323936485</v>
       </c>
       <c r="CZ41" s="62">
         <f t="shared" si="150"/>
-        <v>24.730767930056732</v>
+        <v>38.14943500298569</v>
       </c>
       <c r="DA41" s="62">
         <f t="shared" si="150"/>
-        <v>25.039902529182442</v>
+        <v>38.626302940523011</v>
       </c>
       <c r="DB41" s="62">
         <f t="shared" si="150"/>
-        <v>25.352901310797222</v>
+        <v>39.109131727279546</v>
       </c>
       <c r="DC41" s="62">
         <f t="shared" si="150"/>
-        <v>25.669812577182185</v>
+        <v>39.597995873870538</v>
       </c>
       <c r="DD41" s="62">
         <f t="shared" si="150"/>
-        <v>25.99068523439696</v>
+        <v>40.092970822293921</v>
       </c>
       <c r="DE41" s="62">
         <f t="shared" si="150"/>
-        <v>26.31556879982692</v>
+        <v>40.59413295757259</v>
       </c>
       <c r="DF41" s="62">
         <f t="shared" si="150"/>
-        <v>26.644513409824757</v>
+        <v>41.101559619542243</v>
       </c>
       <c r="DG41" s="62">
         <f t="shared" si="150"/>
-        <v>26.977569827447564</v>
+        <v>41.615329114786519</v>
       </c>
       <c r="DH41" s="62">
         <f t="shared" ref="DH41:ED41" si="151">DG41*(1+$CF$55)</f>
-        <v>27.314789450290657</v>
+        <v>42.135520728721346</v>
       </c>
       <c r="DI41" s="62">
         <f t="shared" si="151"/>
-        <v>27.656224318419291</v>
+        <v>42.662214737830361</v>
       </c>
       <c r="DJ41" s="62">
         <f t="shared" si="151"/>
-        <v>28.001927122399533</v>
+        <v>43.195492422053242</v>
       </c>
       <c r="DK41" s="62">
         <f t="shared" si="151"/>
-        <v>28.351951211429526</v>
+        <v>43.735436077328906</v>
       </c>
       <c r="DL41" s="62">
         <f t="shared" si="151"/>
-        <v>28.706350601572392</v>
+        <v>44.282129028295515</v>
       </c>
       <c r="DM41" s="62">
         <f t="shared" si="151"/>
-        <v>29.065179984092048</v>
+        <v>44.835655641149209</v>
       </c>
       <c r="DN41" s="62">
         <f t="shared" si="151"/>
-        <v>29.428494733893196</v>
+        <v>45.39610133666357</v>
       </c>
       <c r="DO41" s="62">
         <f t="shared" si="151"/>
-        <v>29.79635091806686</v>
+        <v>45.963552603371859</v>
       </c>
       <c r="DP41" s="62">
         <f t="shared" si="151"/>
-        <v>30.168805304542694</v>
+        <v>46.538097010914008</v>
       </c>
       <c r="DQ41" s="62">
         <f t="shared" si="151"/>
-        <v>30.545915370849475</v>
+        <v>47.119823223550434</v>
       </c>
       <c r="DR41" s="62">
         <f t="shared" si="151"/>
-        <v>30.927739312985093</v>
+        <v>47.708821013844812</v>
       </c>
       <c r="DS41" s="62">
         <f t="shared" si="151"/>
-        <v>31.314336054397405</v>
+        <v>48.305181276517871</v>
       </c>
       <c r="DT41" s="62">
         <f t="shared" si="151"/>
-        <v>31.70576525507737</v>
+        <v>48.908996042474342</v>
       </c>
       <c r="DU41" s="62">
         <f t="shared" si="151"/>
-        <v>32.102087320765833</v>
+        <v>49.520358493005268</v>
       </c>
       <c r="DV41" s="62">
         <f t="shared" si="151"/>
-        <v>32.503363412275405</v>
+        <v>50.139362974167831</v>
       </c>
       <c r="DW41" s="62">
         <f t="shared" si="151"/>
-        <v>32.909655454928846</v>
+        <v>50.766105011344926</v>
       </c>
       <c r="DX41" s="62">
         <f t="shared" si="151"/>
-        <v>33.321026148115457</v>
+        <v>51.400681323986738</v>
       </c>
       <c r="DY41" s="62">
         <f t="shared" si="151"/>
-        <v>33.737538974966903</v>
+        <v>52.04318984053657</v>
       </c>
       <c r="DZ41" s="62">
         <f t="shared" si="151"/>
-        <v>34.159258212153986</v>
+        <v>52.693729713543277</v>
       </c>
       <c r="EA41" s="62">
         <f t="shared" si="151"/>
-        <v>34.586248939805913</v>
+        <v>53.352401334962565</v>
       </c>
       <c r="EB41" s="62">
         <f t="shared" si="151"/>
-        <v>35.018577051553486</v>
+        <v>54.019306351649597</v>
       </c>
       <c r="EC41" s="62">
         <f t="shared" si="151"/>
-        <v>35.4563092646979</v>
+        <v>54.694547681045215</v>
       </c>
       <c r="ED41" s="62">
         <f t="shared" si="151"/>
-        <v>35.89951313050662</v>
+        <v>55.378229527058281</v>
       </c>
     </row>
     <row r="42" spans="2:134">
@@ -19227,7 +19269,9 @@
       <c r="AY42" s="48">
         <v>41.173999999999999</v>
       </c>
-      <c r="AZ42" s="48"/>
+      <c r="AZ42" s="48">
+        <v>41.54</v>
+      </c>
       <c r="BK42" s="48">
         <f>AVERAGE(C42:F42)</f>
         <v>35</v>
@@ -19492,9 +19536,9 @@
         <f>AY41/AY42</f>
         <v>-0.26548307184145292</v>
       </c>
-      <c r="AZ43" s="41" t="e">
+      <c r="AZ43" s="41">
         <f>AZ41/AZ42</f>
-        <v>#DIV/0!</v>
+        <v>-0.15269619643716881</v>
       </c>
       <c r="BK43" s="41">
         <f>SUM(C43:F43)</f>
@@ -19546,23 +19590,23 @@
       </c>
       <c r="BW43" s="60">
         <f>BW41/BW42</f>
-        <v>-0.25864360063840325</v>
+        <v>-0.1008809391346628</v>
       </c>
       <c r="BX43" s="60">
         <f>BX41/BX42</f>
-        <v>-6.0996365038858302E-2</v>
+        <v>0.2586010474618734</v>
       </c>
       <c r="BY43" s="60">
         <f t="shared" ref="BY43:BZ43" si="154">BY41/BY42</f>
-        <v>0.17999861775422174</v>
+        <v>0.48242538459210005</v>
       </c>
       <c r="BZ43" s="60">
         <f t="shared" si="154"/>
-        <v>0.41101389610208672</v>
+        <v>0.51593519415177835</v>
       </c>
       <c r="CA43" s="60">
         <f t="shared" ref="CA43" si="155">CA41/CA42</f>
-        <v>0.45208222559772676</v>
+        <v>0.69737751493291456</v>
       </c>
     </row>
     <row r="45" spans="2:134">
@@ -19765,9 +19809,9 @@
         <f>AY28/AY26</f>
         <v>0.55290512607150877</v>
       </c>
-      <c r="AZ45" s="49" t="e">
+      <c r="AZ45" s="49">
         <f>AZ28/AZ26</f>
-        <v>#DIV/0!</v>
+        <v>0.56376683872592226</v>
       </c>
       <c r="BK45" s="49">
         <f t="shared" ref="BK45:BT45" si="158">BK28/BK26</f>
@@ -19820,10 +19864,10 @@
         <v>0.53500000000000003</v>
       </c>
       <c r="BX45" s="59">
-        <v>0.54</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="BY45" s="59">
-        <v>0.54500000000000004</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="BZ45" s="59">
         <v>0.54500000000000004</v>
@@ -20032,9 +20076,9 @@
         <f>AY29/AY26</f>
         <v>8.4756508301303629E-2</v>
       </c>
-      <c r="AZ46" s="49" t="e">
+      <c r="AZ46" s="49">
         <f>AZ29/AZ26</f>
-        <v>#DIV/0!</v>
+        <v>9.76960846027949E-2</v>
       </c>
       <c r="BK46" s="49">
         <f t="shared" ref="BK46:BT46" si="161">BK29/BK26</f>
@@ -20087,16 +20131,16 @@
         <v>9.4E-2</v>
       </c>
       <c r="BX46" s="59">
-        <v>9.2999999999999999E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="BY46" s="59">
-        <v>9.1999999999999998E-2</v>
+        <v>0.09</v>
       </c>
       <c r="BZ46" s="59">
-        <v>9.0999999999999998E-2</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="CA46" s="59">
-        <v>9.0999999999999998E-2</v>
+        <v>8.5999999999999993E-2</v>
       </c>
     </row>
     <row r="47" spans="2:134">
@@ -20299,9 +20343,9 @@
         <f>SUM(AY30:AY31)/AY26</f>
         <v>0.53730633593533295</v>
       </c>
-      <c r="AZ47" s="49" t="e">
+      <c r="AZ47" s="49">
         <f>SUM(AZ30:AZ31)/AZ26</f>
-        <v>#DIV/0!</v>
+        <v>0.46405640186327579</v>
       </c>
       <c r="BK47" s="49">
         <f t="shared" ref="BK47:BT47" si="165">SUM(BK30:BK31)/BK26</f>
@@ -20351,10 +20395,10 @@
         <v>0.4975</v>
       </c>
       <c r="BW47" s="59">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BX47" s="59">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BY47" s="59">
         <v>0.44</v>
@@ -20363,7 +20407,7 @@
         <v>0.42</v>
       </c>
       <c r="CA47" s="59">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="48" spans="2:134">
@@ -20566,9 +20610,9 @@
         <f>AY36/AY26</f>
         <v>-0.14111555784496285</v>
       </c>
-      <c r="AZ48" s="49" t="e">
+      <c r="AZ48" s="49">
         <f>AZ36/AZ26</f>
-        <v>#DIV/0!</v>
+        <v>-7.6923076923076816E-2</v>
       </c>
       <c r="BK48" s="49">
         <f t="shared" ref="BK48:BT48" si="168">BK36/BK26</f>
@@ -20620,23 +20664,23 @@
       </c>
       <c r="BW48" s="59">
         <f t="shared" ref="BW48:BZ48" si="169">BW36/BW26</f>
-        <v>-3.8999999999999903E-2</v>
+        <v>-2.8999999999999925E-2</v>
       </c>
       <c r="BX48" s="59">
         <f t="shared" si="169"/>
-        <v>-1.2999999999999944E-2</v>
+        <v>1.8000000000000075E-2</v>
       </c>
       <c r="BY48" s="59">
         <f t="shared" si="169"/>
-        <v>1.300000000000006E-2</v>
+        <v>3.9999999999999938E-2</v>
       </c>
       <c r="BZ48" s="59">
         <f t="shared" si="169"/>
-        <v>3.4000000000000051E-2</v>
+        <v>3.7000000000000095E-2</v>
       </c>
       <c r="CA48" s="59">
         <f t="shared" ref="CA48" si="170">CA36/CA26</f>
-        <v>3.4000000000000051E-2</v>
+        <v>4.9000000000000106E-2</v>
       </c>
     </row>
     <row r="49" spans="2:134">
@@ -20839,9 +20883,9 @@
         <f>AY40/AY39</f>
         <v>-5.9819620835634179E-3</v>
       </c>
-      <c r="AZ49" s="49" t="e">
+      <c r="AZ49" s="49">
         <f>AZ40/AZ39</f>
-        <v>#DIV/0!</v>
+        <v>-7.8889239507731247E-4</v>
       </c>
       <c r="BK49" s="49">
         <f t="shared" ref="BK49:BT49" si="173">BK40/BK39</f>
@@ -20891,19 +20935,19 @@
         <v>0.12</v>
       </c>
       <c r="BW49" s="59">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="BX49" s="59">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="BY49" s="59">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="BZ49" s="59">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="CA49" s="59">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="50" spans="2:134">
@@ -21106,9 +21150,9 @@
         <f>AY41/AY26</f>
         <v>-0.14437796357200383</v>
       </c>
-      <c r="AZ50" s="49" t="e">
+      <c r="AZ50" s="49">
         <f>AZ41/AZ26</f>
-        <v>#DIV/0!</v>
+        <v>-7.9856477401485479E-2</v>
       </c>
       <c r="BK50" s="49">
         <f t="shared" ref="BK50:BT50" si="176">BK41/BK26</f>
@@ -21160,23 +21204,23 @@
       </c>
       <c r="BW50" s="59">
         <f t="shared" ref="BW50:BZ50" si="177">BW41/BW26</f>
-        <v>-3.4350220562774599E-2</v>
+        <v>-1.3397905462583416E-2</v>
       </c>
       <c r="BX50" s="59">
         <f t="shared" si="177"/>
-        <v>-7.512942591330697E-3</v>
+        <v>3.1851977120297671E-2</v>
       </c>
       <c r="BY50" s="59">
         <f t="shared" si="177"/>
-        <v>2.0823156273482864E-2</v>
+        <v>5.5809423977761397E-2</v>
       </c>
       <c r="BZ50" s="59">
         <f t="shared" si="177"/>
-        <v>4.5000883510125309E-2</v>
+        <v>5.6488454018185662E-2</v>
       </c>
       <c r="CA50" s="59">
         <f t="shared" ref="CA50" si="178">CA41/CA26</f>
-        <v>4.6760924324891782E-2</v>
+        <v>7.2132933690421744E-2</v>
       </c>
     </row>
     <row r="51" spans="2:134">
@@ -21245,7 +21289,9 @@
       <c r="AY52" s="48">
         <v>38.762</v>
       </c>
-      <c r="AZ52" s="48"/>
+      <c r="AZ52" s="48">
+        <v>41.64</v>
+      </c>
       <c r="BR52" s="48">
         <f t="shared" ref="BR52:BR62" si="179">SUM(AH52)</f>
         <v>48.161000000000001</v>
@@ -21268,23 +21314,23 @@
       </c>
       <c r="BW52" s="61">
         <f t="shared" ref="BW52:CA52" si="183">BV52+BW41</f>
-        <v>45.521391614400031</v>
+        <v>51.847674340700024</v>
       </c>
       <c r="BX52" s="61">
         <f t="shared" si="183"/>
-        <v>43.07543737634181</v>
+        <v>62.217576343921145</v>
       </c>
       <c r="BY52" s="61">
         <f t="shared" si="183"/>
-        <v>50.293381948286104</v>
+        <v>81.562834266064357</v>
       </c>
       <c r="BZ52" s="61">
         <f t="shared" si="183"/>
-        <v>66.775039181979778</v>
+        <v>102.25183555155067</v>
       </c>
       <c r="CA52" s="61">
         <f t="shared" si="183"/>
-        <v>84.903536428448618</v>
+        <v>130.21667390036055</v>
       </c>
     </row>
     <row r="53" spans="2:134" ht="15" customHeight="1">
@@ -21350,7 +21396,9 @@
       <c r="AY53" s="48">
         <v>42.64</v>
       </c>
-      <c r="AZ53" s="48"/>
+      <c r="AZ53" s="48">
+        <v>44.4</v>
+      </c>
       <c r="BR53" s="48">
         <f t="shared" si="179"/>
         <v>35.405000000000001</v>
@@ -21435,7 +21483,9 @@
       <c r="AY54" s="48">
         <v>62.255000000000003</v>
       </c>
-      <c r="AZ54" s="48"/>
+      <c r="AZ54" s="48">
+        <v>65.56</v>
+      </c>
       <c r="BR54" s="48">
         <f t="shared" si="179"/>
         <v>48.613999999999997</v>
@@ -21456,24 +21506,24 @@
         <f t="shared" si="184"/>
         <v>62.006</v>
       </c>
-      <c r="BX54" s="73" t="s">
+      <c r="BX54" s="72" t="s">
         <v>1349</v>
       </c>
-      <c r="BY54" s="74"/>
-      <c r="BZ54" s="74"/>
-      <c r="CA54" s="73" t="s">
+      <c r="BY54" s="73"/>
+      <c r="BZ54" s="73"/>
+      <c r="CA54" s="72" t="s">
         <v>1350</v>
       </c>
-      <c r="CB54" s="74"/>
-      <c r="CC54" s="75" t="s">
+      <c r="CB54" s="73"/>
+      <c r="CC54" s="74" t="s">
         <v>1351</v>
       </c>
-      <c r="CD54" s="74"/>
+      <c r="CD54" s="73"/>
       <c r="CE54" s="63" t="s">
         <v>254</v>
       </c>
       <c r="CF54" s="64">
-        <v>4.4999999999999998E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="CI54" s="36" t="s">
         <v>255</v>
@@ -21542,7 +21592,9 @@
       <c r="AY55" s="48">
         <v>0</v>
       </c>
-      <c r="AZ55" s="48"/>
+      <c r="AZ55" s="48">
+        <v>9.6999999999999993</v>
+      </c>
       <c r="BR55" s="48">
         <f t="shared" si="179"/>
         <v>8.6989999999999998</v>
@@ -21563,21 +21615,21 @@
         <f t="shared" si="184"/>
         <v>0</v>
       </c>
-      <c r="BX55" s="74">
+      <c r="BX55" s="73">
         <v>2025</v>
       </c>
-      <c r="BY55" s="74"/>
-      <c r="BZ55" s="74">
+      <c r="BY55" s="73"/>
+      <c r="BZ55" s="73">
         <v>2024</v>
       </c>
-      <c r="CA55" s="74">
+      <c r="CA55" s="73">
         <v>2025</v>
       </c>
-      <c r="CB55" s="74"/>
-      <c r="CC55" s="75" t="s">
+      <c r="CB55" s="73"/>
+      <c r="CC55" s="74" t="s">
         <v>1352</v>
       </c>
-      <c r="CD55" s="74"/>
+      <c r="CD55" s="73"/>
       <c r="CE55" s="63" t="s">
         <v>257</v>
       </c>
@@ -21648,7 +21700,9 @@
       <c r="AY56" s="48">
         <v>12.996</v>
       </c>
-      <c r="AZ56" s="48"/>
+      <c r="AZ56" s="48">
+        <v>30.52</v>
+      </c>
       <c r="BR56" s="48">
         <f t="shared" si="179"/>
         <v>0</v>
@@ -21669,29 +21723,29 @@
         <f t="shared" si="184"/>
         <v>7.5350000000000001</v>
       </c>
-      <c r="BX56" s="76">
+      <c r="BX56" s="75">
         <f>AVERAGE(BV36)*(1-BV49)</f>
         <v>-35.156879999999994</v>
       </c>
-      <c r="BY56" s="74"/>
-      <c r="BZ56" s="77">
+      <c r="BY56" s="73"/>
+      <c r="BZ56" s="76">
         <f>SUM(BU52:BU54)-BU64+BU57+BU59+BU58</f>
         <v>255.571</v>
       </c>
-      <c r="CA56" s="77">
+      <c r="CA56" s="76">
         <f>SUM(BV52:BV54)-BV64+BV57+BV59+BV58</f>
         <v>228.91399999999999</v>
       </c>
-      <c r="CC56" s="77">
+      <c r="CC56" s="76">
         <f>AVERAGE(BZ56:CA56)</f>
         <v>242.24250000000001</v>
       </c>
-      <c r="CD56" s="74"/>
+      <c r="CD56" s="73"/>
       <c r="CE56" s="63" t="s">
         <v>259</v>
       </c>
       <c r="CF56" s="64">
-        <v>4.5100000000000001E-2</v>
+        <v>4.1599999999999998E-2</v>
       </c>
     </row>
     <row r="57" spans="2:134" ht="15" customHeight="1">
@@ -21757,7 +21811,9 @@
       <c r="AY57" s="48">
         <v>31.065999999999999</v>
       </c>
-      <c r="AZ57" s="48"/>
+      <c r="AZ57" s="48">
+        <v>66.731999999999999</v>
+      </c>
       <c r="BR57" s="48">
         <f t="shared" si="179"/>
         <v>37.073</v>
@@ -21778,22 +21834,22 @@
         <f t="shared" si="184"/>
         <v>32.299999999999997</v>
       </c>
-      <c r="BX57" s="78">
+      <c r="BX57" s="77">
         <f>BX56/CC56</f>
         <v>-0.14513093284621811</v>
       </c>
-      <c r="BY57" s="74"/>
-      <c r="BZ57" s="74"/>
-      <c r="CA57" s="74"/>
-      <c r="CB57" s="74"/>
-      <c r="CC57" s="74"/>
-      <c r="CD57" s="74"/>
+      <c r="BY57" s="73"/>
+      <c r="BZ57" s="73"/>
+      <c r="CA57" s="73"/>
+      <c r="CB57" s="73"/>
+      <c r="CC57" s="73"/>
+      <c r="CD57" s="73"/>
       <c r="CE57" s="63" t="s">
         <v>261</v>
       </c>
       <c r="CF57" s="64">
         <f>7.5%-CF56</f>
-        <v>2.9899999999999996E-2</v>
+        <v>3.3399999999999999E-2</v>
       </c>
     </row>
     <row r="58" spans="2:134" ht="15" customHeight="1">
@@ -21859,7 +21915,9 @@
       <c r="AY58" s="48">
         <v>68.38</v>
       </c>
-      <c r="AZ58" s="48"/>
+      <c r="AZ58" s="48">
+        <v>11</v>
+      </c>
       <c r="BR58" s="48">
         <f t="shared" si="179"/>
         <v>168.977</v>
@@ -21951,7 +22009,9 @@
       <c r="AY59" s="48">
         <v>0</v>
       </c>
-      <c r="AZ59" s="48"/>
+      <c r="AZ59" s="48">
+        <v>29.85</v>
+      </c>
       <c r="BR59" s="48">
         <f t="shared" si="179"/>
         <v>201.316</v>
@@ -21977,7 +22037,7 @@
       </c>
       <c r="CF59" s="64">
         <f>+CF56+(CF57*CF58)</f>
-        <v>6.3638E-2</v>
+        <v>6.2308000000000002E-2</v>
       </c>
     </row>
     <row r="60" spans="2:134" ht="15" customHeight="1">
@@ -22043,7 +22103,9 @@
       <c r="AY60" s="48">
         <v>9.5399999999999991</v>
       </c>
-      <c r="AZ60" s="48"/>
+      <c r="AZ60" s="48">
+        <v>6.72</v>
+      </c>
       <c r="BR60" s="48">
         <f t="shared" si="179"/>
         <v>13.193</v>
@@ -22129,7 +22191,9 @@
       <c r="AY61" s="48">
         <v>0</v>
       </c>
-      <c r="AZ61" s="48"/>
+      <c r="AZ61" s="48">
+        <v>4.33</v>
+      </c>
       <c r="BR61" s="48">
         <f t="shared" si="179"/>
         <v>0</v>
@@ -22155,7 +22219,7 @@
       </c>
       <c r="CF61" s="61">
         <f>NPV(CF59,BV41:DS41)</f>
-        <v>206.6346161328855</v>
+        <v>370.74937138848304</v>
       </c>
     </row>
     <row r="62" spans="2:134" s="2" customFormat="1" ht="15" customHeight="1">
@@ -22241,7 +22305,7 @@
       </c>
       <c r="AZ62" s="50">
         <f>SUM(AZ52:AZ61)</f>
-        <v>0</v>
+        <v>310.45200000000006</v>
       </c>
       <c r="BA62" s="35"/>
       <c r="BB62" s="35"/>
@@ -22336,7 +22400,7 @@
       </c>
       <c r="CF63" s="60">
         <f>CF61/CF62</f>
-        <v>5.0166209306357246</v>
+        <v>9.0009558482273135</v>
       </c>
       <c r="CG63" s="66"/>
     </row>
@@ -22401,7 +22465,9 @@
       <c r="AY64" s="48">
         <v>31.882000000000001</v>
       </c>
-      <c r="AZ64" s="48"/>
+      <c r="AZ64" s="48">
+        <v>35.39</v>
+      </c>
       <c r="BR64" s="48">
         <f t="shared" ref="BR64:BR74" si="186">SUM(AH64)</f>
         <v>19.63</v>
@@ -22427,7 +22493,7 @@
       </c>
       <c r="CF64" s="60">
         <f>Main!C5</f>
-        <v>13.33</v>
+        <v>9.99</v>
       </c>
       <c r="CG64" s="67"/>
     </row>
@@ -22492,7 +22558,9 @@
       <c r="AY65" s="48">
         <v>27.657</v>
       </c>
-      <c r="AZ65" s="48"/>
+      <c r="AZ65" s="48">
+        <v>29.85</v>
+      </c>
       <c r="BR65" s="48">
         <f t="shared" si="186"/>
         <v>35.459000000000003</v>
@@ -22516,9 +22584,9 @@
       <c r="CE65" s="63" t="s">
         <v>274</v>
       </c>
-      <c r="CF65" s="68">
+      <c r="CF65" s="64">
         <f>CF63/CF64-1</f>
-        <v>-0.62365934503858034</v>
+        <v>-9.9003418595864479E-2</v>
       </c>
       <c r="CG65" s="66" t="str">
         <f>IF(CF65&gt;0,"Upside","Downside")</f>
@@ -22586,7 +22654,9 @@
       <c r="AY66" s="48">
         <v>0</v>
       </c>
-      <c r="AZ66" s="48"/>
+      <c r="AZ66" s="48">
+        <v>0</v>
+      </c>
       <c r="BR66" s="48">
         <f t="shared" si="186"/>
         <v>0</v>
@@ -22607,11 +22677,11 @@
         <f t="shared" si="190"/>
         <v>0</v>
       </c>
-      <c r="CE66" s="84" t="str" cm="1">
+      <c r="CE66" s="83" t="str" cm="1">
         <f t="array" ref="CE66">_xlfn.IFS(CF65&gt;=25%,"Strong Buy",CF65&gt;=10.00001%,"Buy",AND(CF65&lt;=10%,CF65&gt;=-4.9999%),"Hold",AND(CF65&lt;=-5%,CF65&gt;=-14.999999%),"Sell",CF65&lt;=-15%,"Strong Sell")</f>
-        <v>Strong Sell</v>
-      </c>
-      <c r="CF66" s="84"/>
+        <v>Sell</v>
+      </c>
+      <c r="CF66" s="83"/>
     </row>
     <row r="67" spans="2:134" ht="15" customHeight="1">
       <c r="B67" s="1" t="s">
@@ -22674,7 +22744,9 @@
       <c r="AY67" s="48">
         <v>8.7430000000000003</v>
       </c>
-      <c r="AZ67" s="48"/>
+      <c r="AZ67" s="48">
+        <v>6.72</v>
+      </c>
       <c r="BR67" s="48">
         <f t="shared" si="186"/>
         <v>2.4950000000000001</v>
@@ -22757,7 +22829,9 @@
       <c r="AY68" s="48">
         <v>0</v>
       </c>
-      <c r="AZ68" s="48"/>
+      <c r="AZ68" s="48">
+        <v>0</v>
+      </c>
       <c r="BR68" s="48">
         <f t="shared" si="186"/>
         <v>20</v>
@@ -22840,7 +22914,9 @@
       <c r="AY69" s="48">
         <v>4.2679999999999998</v>
       </c>
-      <c r="AZ69" s="48"/>
+      <c r="AZ69" s="48">
+        <v>4.33</v>
+      </c>
       <c r="BR69" s="48">
         <f t="shared" si="186"/>
         <v>19.954999999999998</v>
@@ -22923,7 +22999,9 @@
       <c r="AY70" s="48">
         <v>0</v>
       </c>
-      <c r="AZ70" s="48"/>
+      <c r="AZ70" s="48">
+        <v>0</v>
+      </c>
       <c r="BR70" s="48">
         <f t="shared" si="186"/>
         <v>15.741</v>
@@ -23006,7 +23084,9 @@
       <c r="AY71" s="48">
         <v>14.237</v>
       </c>
-      <c r="AZ71" s="48"/>
+      <c r="AZ71" s="48">
+        <v>17.05</v>
+      </c>
       <c r="BR71" s="48">
         <f t="shared" si="186"/>
         <v>8.7010000000000005</v>
@@ -23109,7 +23189,7 @@
       </c>
       <c r="AZ72" s="50">
         <f t="shared" si="193"/>
-        <v>0</v>
+        <v>93.34</v>
       </c>
       <c r="BA72" s="35"/>
       <c r="BB72" s="35"/>
@@ -23259,7 +23339,9 @@
       <c r="AY73" s="48">
         <v>178.85499999999999</v>
       </c>
-      <c r="AZ73" s="48"/>
+      <c r="AZ73" s="48">
+        <v>176.33</v>
+      </c>
       <c r="BR73" s="48">
         <f t="shared" si="186"/>
         <v>439.45699999999999</v>
@@ -23362,7 +23444,7 @@
       </c>
       <c r="AZ74" s="50">
         <f>AZ72+AZ73</f>
-        <v>0</v>
+        <v>269.67</v>
       </c>
       <c r="BA74" s="35"/>
       <c r="BB74" s="35"/>
@@ -23528,9 +23610,9 @@
         <f>SUM(AY52:AY55)/SUM(AY64:AY67)</f>
         <v>2.1038780352069364</v>
       </c>
-      <c r="AZ76" s="41" t="e">
+      <c r="AZ76" s="41">
         <f>SUM(AZ52:AZ55)/SUM(AZ64:AZ67)</f>
-        <v>#DIV/0!</v>
+        <v>2.241523068371317</v>
       </c>
       <c r="BQ76" s="48"/>
       <c r="BR76" s="48">
@@ -23630,9 +23712,9 @@
         <f>(SUM(AY52:AY55)-AY54)/SUM(AY64:AY67)</f>
         <v>1.1921443425793037</v>
       </c>
-      <c r="AZ77" s="41" t="e">
+      <c r="AZ77" s="41">
         <f>(SUM(AZ52:AZ55)-AZ54)/SUM(AZ64:AZ67)</f>
-        <v>#DIV/0!</v>
+        <v>1.3304613674263475</v>
       </c>
       <c r="BQ77" s="48"/>
       <c r="BR77" s="48">
@@ -23732,9 +23814,9 @@
         <f>AY52/SUM(AY64:AY67)</f>
         <v>0.56767522919656721</v>
       </c>
-      <c r="AZ78" s="41" t="e">
+      <c r="AZ78" s="41">
         <f>AZ52/SUM(AZ64:AZ67)</f>
-        <v>#DIV/0!</v>
+        <v>0.57865480822679261</v>
       </c>
       <c r="BQ78" s="48"/>
       <c r="BR78" s="48">
@@ -23834,9 +23916,9 @@
         <f>AY26/AY62</f>
         <v>0.28501462511152353</v>
       </c>
-      <c r="AZ79" s="41" t="e">
+      <c r="AZ79" s="41">
         <f>AZ26/AZ62</f>
-        <v>#DIV/0!</v>
+        <v>0.25585275662582296</v>
       </c>
       <c r="BQ79" s="48"/>
       <c r="BR79" s="48">
@@ -23938,7 +24020,7 @@
       </c>
       <c r="AZ80" s="41">
         <f>AZ54/AVERAGE(AW27:AZ27)</f>
-        <v>0</v>
+        <v>1.87873343105269</v>
       </c>
       <c r="BQ80" s="48"/>
       <c r="BR80" s="48">
@@ -24038,9 +24120,9 @@
         <f>AY41/AY74</f>
         <v>-4.1149366440547744E-2</v>
       </c>
-      <c r="AZ81" s="49" t="e">
+      <c r="AZ81" s="49">
         <f>AZ41/AZ74</f>
-        <v>#DIV/0!</v>
+        <v>-2.3521340898134725E-2</v>
       </c>
       <c r="BQ81" s="49"/>
       <c r="BR81" s="49">
@@ -24140,9 +24222,9 @@
         <f>AY41/AY73</f>
         <v>-6.1116546923485414E-2</v>
       </c>
-      <c r="AZ82" s="49" t="e">
+      <c r="AZ82" s="49">
         <f>AZ41/AZ73</f>
-        <v>#DIV/0!</v>
+        <v>-3.5972324618612779E-2</v>
       </c>
       <c r="BQ82" s="49"/>
       <c r="BR82" s="49">
@@ -24368,7 +24450,7 @@
       </c>
       <c r="AZ84" s="48">
         <f t="shared" ref="AZ84" si="224">AZ41</f>
-        <v>0</v>
+        <v>-6.342999999999992</v>
       </c>
       <c r="BK84" s="48">
         <f t="shared" ref="BK84:BU84" si="225">BK41</f>
@@ -24571,7 +24653,10 @@
       <c r="AY85" s="50">
         <v>-15.914</v>
       </c>
-      <c r="AZ85" s="50"/>
+      <c r="AZ85" s="50">
+        <f>-11.25-AY85</f>
+        <v>4.6639999999999997</v>
+      </c>
       <c r="BA85" s="35"/>
       <c r="BB85" s="35"/>
       <c r="BC85" s="35"/>
@@ -24837,7 +24922,10 @@
       <c r="AY86" s="48">
         <v>-0.73099999999999998</v>
       </c>
-      <c r="AZ86" s="48"/>
+      <c r="AZ86" s="48">
+        <f>-1.15-AY86</f>
+        <v>-0.41899999999999993</v>
+      </c>
       <c r="BA86" s="51"/>
       <c r="BB86" s="51"/>
       <c r="BC86" s="51"/>
@@ -25094,7 +25182,7 @@
       </c>
       <c r="AZ87" s="50">
         <f t="shared" ref="AZ87" si="229">AZ85+AZ86</f>
-        <v>0</v>
+        <v>4.2450000000000001</v>
       </c>
       <c r="BA87" s="35"/>
       <c r="BB87" s="35"/>
@@ -25413,7 +25501,7 @@
       </c>
       <c r="AZ88" s="48">
         <f t="shared" ref="AZ88" si="233">AZ42</f>
-        <v>0</v>
+        <v>41.54</v>
       </c>
       <c r="BK88" s="48">
         <f>AVERAGE(C88:F88)</f>
@@ -25663,9 +25751,9 @@
         <f t="shared" si="235"/>
         <v>-0.40425996988390733</v>
       </c>
-      <c r="AZ89" s="41" t="e">
+      <c r="AZ89" s="41">
         <f t="shared" ref="AZ89" si="236">AZ87/AZ88</f>
-        <v>#DIV/0!</v>
+        <v>0.10219065960519981</v>
       </c>
       <c r="BK89" s="41">
         <f t="shared" ref="BK89:BT89" si="237">BK87/BK88</f>
@@ -25750,7 +25838,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="AO36:AS36 R39 AL62 AW62 AX72 BV88" formula="1"/>
-    <ignoredError sqref="AE47:AW51 AE43:AH43 AE32:AH32 AE33:AH35 AE38:AH38 AE42:AH42 S39:AH39 C27:AH30 C26:AG26 C36:AH37 C31:AH31 C40:AH41 C39:Q39 BK27:BR41 BK43:BR43 BU86 BK85:BT85 BK86:BL86 BN86:BT86 AT62:AV62 AW76:AW78 AH79:AW79 AH76:AV78 AX76:AX79 AX85:AX86 AY47 AY76:AY78 BK26:BR26 BV42" formulaRange="1"/>
+    <ignoredError sqref="AE47:AW51 AE43:AH43 AE32:AH32 AE33:AH35 AE38:AH38 AE42:AH42 S39:AH39 C27:AH30 C26:AG26 C36:AH37 C31:AH31 C40:AH41 C39:Q39 BK27:BR41 BK43:BR43 BU86 BK85:BT85 BK86:BL86 BN86:BT86 AT62:AV62 AW76:AW78 AH79:AW79 AH76:AV78 AX76:AX79 AX85:AX86 AY47 AY76:AY78 BK26:BR26 BV42 AZ76:AZ82" formulaRange="1"/>
     <ignoredError sqref="AH26 BS42:BU42 BK42:BR42 AP62 AI62 AX62" formula="1" formulaRange="1"/>
     <ignoredError sqref="C43:AD43" evalError="1" formulaRange="1"/>
     <ignoredError sqref="AZ89 AZ23:AZ24" evalError="1"/>

--- a/ANGO_Model.xlsx
+++ b/ANGO_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Health Care\MedTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB96907A-6321-435C-B6C9-CDCC1F58C5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DA76BD-1E67-4E5E-8F52-AA9AA60F7E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="390" windowWidth="29010" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4795,10 +4795,10 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -9888,8 +9888,20 @@
       <sheetName val="Debt Schedule"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0">
+        <row r="5">
+          <cell r="C5">
+            <v>367.54</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="79">
+          <cell r="CZ79">
+            <v>409.93116237430775</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="2">
         <row r="188">
           <cell r="I188" t="str">
@@ -10060,7 +10072,7 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Main | Overview"/>
+      <sheetName val="Main"/>
       <sheetName val="Model"/>
       <sheetName val="Notes | Quant Analysis"/>
       <sheetName val="Interventional Cardiology"/>
@@ -10069,9 +10081,17 @@
       <sheetName val="Management"/>
       <sheetName val="Debt Schedule"/>
       <sheetName val="Clinical Trial Channel"/>
+      <sheetName val="Main | Overview"/>
+      <sheetName val="Markets | Product Lines"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="C3">
+            <v>98.22</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="AW3" t="str">
@@ -10146,6 +10166,8 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -11246,114 +11268,114 @@
       <c r="C86" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D86" s="81" t="s">
+      <c r="D86" s="80" t="s">
         <v>117</v>
       </c>
-      <c r="E86" s="81"/>
-      <c r="F86" s="81"/>
-      <c r="G86" s="81"/>
-      <c r="H86" s="81"/>
-      <c r="I86" s="81"/>
-      <c r="J86" s="81"/>
-      <c r="K86" s="81"/>
-      <c r="L86" s="81"/>
-      <c r="M86" s="81"/>
-      <c r="N86" s="81"/>
-      <c r="O86" s="81"/>
-      <c r="P86" s="81"/>
-      <c r="Q86" s="81"/>
-      <c r="R86" s="81"/>
-      <c r="S86" s="81"/>
-      <c r="T86" s="81"/>
-      <c r="U86" s="81"/>
-      <c r="V86" s="81"/>
-      <c r="W86" s="81"/>
-      <c r="X86" s="81"/>
-      <c r="Y86" s="81"/>
+      <c r="E86" s="80"/>
+      <c r="F86" s="80"/>
+      <c r="G86" s="80"/>
+      <c r="H86" s="80"/>
+      <c r="I86" s="80"/>
+      <c r="J86" s="80"/>
+      <c r="K86" s="80"/>
+      <c r="L86" s="80"/>
+      <c r="M86" s="80"/>
+      <c r="N86" s="80"/>
+      <c r="O86" s="80"/>
+      <c r="P86" s="80"/>
+      <c r="Q86" s="80"/>
+      <c r="R86" s="80"/>
+      <c r="S86" s="80"/>
+      <c r="T86" s="80"/>
+      <c r="U86" s="80"/>
+      <c r="V86" s="80"/>
+      <c r="W86" s="80"/>
+      <c r="X86" s="80"/>
+      <c r="Y86" s="80"/>
       <c r="Z86" s="56"/>
       <c r="AA86" s="56"/>
       <c r="AB86" s="56"/>
     </row>
     <row r="87" spans="3:28">
       <c r="C87" s="29"/>
-      <c r="D87" s="81"/>
-      <c r="E87" s="81"/>
-      <c r="F87" s="81"/>
-      <c r="G87" s="81"/>
-      <c r="H87" s="81"/>
-      <c r="I87" s="81"/>
-      <c r="J87" s="81"/>
-      <c r="K87" s="81"/>
-      <c r="L87" s="81"/>
-      <c r="M87" s="81"/>
-      <c r="N87" s="81"/>
-      <c r="O87" s="81"/>
-      <c r="P87" s="81"/>
-      <c r="Q87" s="81"/>
-      <c r="R87" s="81"/>
-      <c r="S87" s="81"/>
-      <c r="T87" s="81"/>
-      <c r="U87" s="81"/>
-      <c r="V87" s="81"/>
-      <c r="W87" s="81"/>
-      <c r="X87" s="81"/>
-      <c r="Y87" s="81"/>
+      <c r="D87" s="80"/>
+      <c r="E87" s="80"/>
+      <c r="F87" s="80"/>
+      <c r="G87" s="80"/>
+      <c r="H87" s="80"/>
+      <c r="I87" s="80"/>
+      <c r="J87" s="80"/>
+      <c r="K87" s="80"/>
+      <c r="L87" s="80"/>
+      <c r="M87" s="80"/>
+      <c r="N87" s="80"/>
+      <c r="O87" s="80"/>
+      <c r="P87" s="80"/>
+      <c r="Q87" s="80"/>
+      <c r="R87" s="80"/>
+      <c r="S87" s="80"/>
+      <c r="T87" s="80"/>
+      <c r="U87" s="80"/>
+      <c r="V87" s="80"/>
+      <c r="W87" s="80"/>
+      <c r="X87" s="80"/>
+      <c r="Y87" s="80"/>
       <c r="Z87" s="56"/>
       <c r="AA87" s="56"/>
       <c r="AB87" s="56"/>
     </row>
     <row r="88" spans="3:28">
       <c r="C88" s="29"/>
-      <c r="D88" s="81"/>
-      <c r="E88" s="81"/>
-      <c r="F88" s="81"/>
-      <c r="G88" s="81"/>
-      <c r="H88" s="81"/>
-      <c r="I88" s="81"/>
-      <c r="J88" s="81"/>
-      <c r="K88" s="81"/>
-      <c r="L88" s="81"/>
-      <c r="M88" s="81"/>
-      <c r="N88" s="81"/>
-      <c r="O88" s="81"/>
-      <c r="P88" s="81"/>
-      <c r="Q88" s="81"/>
-      <c r="R88" s="81"/>
-      <c r="S88" s="81"/>
-      <c r="T88" s="81"/>
-      <c r="U88" s="81"/>
-      <c r="V88" s="81"/>
-      <c r="W88" s="81"/>
-      <c r="X88" s="81"/>
-      <c r="Y88" s="81"/>
+      <c r="D88" s="80"/>
+      <c r="E88" s="80"/>
+      <c r="F88" s="80"/>
+      <c r="G88" s="80"/>
+      <c r="H88" s="80"/>
+      <c r="I88" s="80"/>
+      <c r="J88" s="80"/>
+      <c r="K88" s="80"/>
+      <c r="L88" s="80"/>
+      <c r="M88" s="80"/>
+      <c r="N88" s="80"/>
+      <c r="O88" s="80"/>
+      <c r="P88" s="80"/>
+      <c r="Q88" s="80"/>
+      <c r="R88" s="80"/>
+      <c r="S88" s="80"/>
+      <c r="T88" s="80"/>
+      <c r="U88" s="80"/>
+      <c r="V88" s="80"/>
+      <c r="W88" s="80"/>
+      <c r="X88" s="80"/>
+      <c r="Y88" s="80"/>
       <c r="Z88" s="56"/>
       <c r="AA88" s="56"/>
       <c r="AB88" s="56"/>
     </row>
     <row r="89" spans="3:28">
       <c r="C89" s="29"/>
-      <c r="D89" s="81"/>
-      <c r="E89" s="81"/>
-      <c r="F89" s="81"/>
-      <c r="G89" s="81"/>
-      <c r="H89" s="81"/>
-      <c r="I89" s="81"/>
-      <c r="J89" s="81"/>
-      <c r="K89" s="81"/>
-      <c r="L89" s="81"/>
-      <c r="M89" s="81"/>
-      <c r="N89" s="81"/>
-      <c r="O89" s="81"/>
-      <c r="P89" s="81"/>
-      <c r="Q89" s="81"/>
-      <c r="R89" s="81"/>
-      <c r="S89" s="81"/>
-      <c r="T89" s="81"/>
-      <c r="U89" s="81"/>
-      <c r="V89" s="81"/>
-      <c r="W89" s="81"/>
-      <c r="X89" s="81"/>
-      <c r="Y89" s="81"/>
+      <c r="D89" s="80"/>
+      <c r="E89" s="80"/>
+      <c r="F89" s="80"/>
+      <c r="G89" s="80"/>
+      <c r="H89" s="80"/>
+      <c r="I89" s="80"/>
+      <c r="J89" s="80"/>
+      <c r="K89" s="80"/>
+      <c r="L89" s="80"/>
+      <c r="M89" s="80"/>
+      <c r="N89" s="80"/>
+      <c r="O89" s="80"/>
+      <c r="P89" s="80"/>
+      <c r="Q89" s="80"/>
+      <c r="R89" s="80"/>
+      <c r="S89" s="80"/>
+      <c r="T89" s="80"/>
+      <c r="U89" s="80"/>
+      <c r="V89" s="80"/>
+      <c r="W89" s="80"/>
+      <c r="X89" s="80"/>
+      <c r="Y89" s="80"/>
       <c r="Z89" s="56"/>
       <c r="AA89" s="56"/>
       <c r="AB89" s="56"/>
@@ -11362,78 +11384,78 @@
       <c r="C90" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D90" s="81" t="s">
+      <c r="D90" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="E90" s="81"/>
-      <c r="F90" s="81"/>
-      <c r="G90" s="81"/>
-      <c r="H90" s="81"/>
-      <c r="I90" s="81"/>
-      <c r="J90" s="81"/>
-      <c r="K90" s="81"/>
-      <c r="L90" s="81"/>
-      <c r="M90" s="81"/>
-      <c r="N90" s="81"/>
-      <c r="O90" s="81"/>
-      <c r="P90" s="81"/>
-      <c r="Q90" s="81"/>
-      <c r="R90" s="81"/>
-      <c r="S90" s="81"/>
-      <c r="T90" s="81"/>
-      <c r="U90" s="81"/>
-      <c r="V90" s="81"/>
-      <c r="W90" s="81"/>
-      <c r="X90" s="81"/>
-      <c r="Y90" s="81"/>
+      <c r="E90" s="80"/>
+      <c r="F90" s="80"/>
+      <c r="G90" s="80"/>
+      <c r="H90" s="80"/>
+      <c r="I90" s="80"/>
+      <c r="J90" s="80"/>
+      <c r="K90" s="80"/>
+      <c r="L90" s="80"/>
+      <c r="M90" s="80"/>
+      <c r="N90" s="80"/>
+      <c r="O90" s="80"/>
+      <c r="P90" s="80"/>
+      <c r="Q90" s="80"/>
+      <c r="R90" s="80"/>
+      <c r="S90" s="80"/>
+      <c r="T90" s="80"/>
+      <c r="U90" s="80"/>
+      <c r="V90" s="80"/>
+      <c r="W90" s="80"/>
+      <c r="X90" s="80"/>
+      <c r="Y90" s="80"/>
     </row>
     <row r="91" spans="3:28">
-      <c r="D91" s="81"/>
-      <c r="E91" s="81"/>
-      <c r="F91" s="81"/>
-      <c r="G91" s="81"/>
-      <c r="H91" s="81"/>
-      <c r="I91" s="81"/>
-      <c r="J91" s="81"/>
-      <c r="K91" s="81"/>
-      <c r="L91" s="81"/>
-      <c r="M91" s="81"/>
-      <c r="N91" s="81"/>
-      <c r="O91" s="81"/>
-      <c r="P91" s="81"/>
-      <c r="Q91" s="81"/>
-      <c r="R91" s="81"/>
-      <c r="S91" s="81"/>
-      <c r="T91" s="81"/>
-      <c r="U91" s="81"/>
-      <c r="V91" s="81"/>
-      <c r="W91" s="81"/>
-      <c r="X91" s="81"/>
-      <c r="Y91" s="81"/>
+      <c r="D91" s="80"/>
+      <c r="E91" s="80"/>
+      <c r="F91" s="80"/>
+      <c r="G91" s="80"/>
+      <c r="H91" s="80"/>
+      <c r="I91" s="80"/>
+      <c r="J91" s="80"/>
+      <c r="K91" s="80"/>
+      <c r="L91" s="80"/>
+      <c r="M91" s="80"/>
+      <c r="N91" s="80"/>
+      <c r="O91" s="80"/>
+      <c r="P91" s="80"/>
+      <c r="Q91" s="80"/>
+      <c r="R91" s="80"/>
+      <c r="S91" s="80"/>
+      <c r="T91" s="80"/>
+      <c r="U91" s="80"/>
+      <c r="V91" s="80"/>
+      <c r="W91" s="80"/>
+      <c r="X91" s="80"/>
+      <c r="Y91" s="80"/>
     </row>
     <row r="92" spans="3:28">
-      <c r="D92" s="81"/>
-      <c r="E92" s="81"/>
-      <c r="F92" s="81"/>
-      <c r="G92" s="81"/>
-      <c r="H92" s="81"/>
-      <c r="I92" s="81"/>
-      <c r="J92" s="81"/>
-      <c r="K92" s="81"/>
-      <c r="L92" s="81"/>
-      <c r="M92" s="81"/>
-      <c r="N92" s="81"/>
-      <c r="O92" s="81"/>
-      <c r="P92" s="81"/>
-      <c r="Q92" s="81"/>
-      <c r="R92" s="81"/>
-      <c r="S92" s="81"/>
-      <c r="T92" s="81"/>
-      <c r="U92" s="81"/>
-      <c r="V92" s="81"/>
-      <c r="W92" s="81"/>
-      <c r="X92" s="81"/>
-      <c r="Y92" s="81"/>
+      <c r="D92" s="80"/>
+      <c r="E92" s="80"/>
+      <c r="F92" s="80"/>
+      <c r="G92" s="80"/>
+      <c r="H92" s="80"/>
+      <c r="I92" s="80"/>
+      <c r="J92" s="80"/>
+      <c r="K92" s="80"/>
+      <c r="L92" s="80"/>
+      <c r="M92" s="80"/>
+      <c r="N92" s="80"/>
+      <c r="O92" s="80"/>
+      <c r="P92" s="80"/>
+      <c r="Q92" s="80"/>
+      <c r="R92" s="80"/>
+      <c r="S92" s="80"/>
+      <c r="T92" s="80"/>
+      <c r="U92" s="80"/>
+      <c r="V92" s="80"/>
+      <c r="W92" s="80"/>
+      <c r="X92" s="80"/>
+      <c r="Y92" s="80"/>
     </row>
     <row r="93" spans="3:28">
       <c r="C93" s="1" t="s">
@@ -11463,104 +11485,104 @@
       <c r="Y93" s="57"/>
     </row>
     <row r="94" spans="3:28">
-      <c r="D94" s="80" t="s">
+      <c r="D94" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="E94" s="80"/>
-      <c r="F94" s="80"/>
-      <c r="G94" s="80"/>
-      <c r="H94" s="80"/>
-      <c r="I94" s="80"/>
-      <c r="J94" s="80"/>
-      <c r="K94" s="80"/>
-      <c r="L94" s="80"/>
-      <c r="M94" s="80"/>
-      <c r="N94" s="80"/>
-      <c r="O94" s="80"/>
-      <c r="P94" s="80"/>
-      <c r="Q94" s="80"/>
-      <c r="R94" s="80"/>
-      <c r="S94" s="80"/>
-      <c r="T94" s="80"/>
-      <c r="U94" s="80"/>
-      <c r="V94" s="80"/>
-      <c r="W94" s="80"/>
-      <c r="X94" s="80"/>
-      <c r="Y94" s="80"/>
+      <c r="E94" s="81"/>
+      <c r="F94" s="81"/>
+      <c r="G94" s="81"/>
+      <c r="H94" s="81"/>
+      <c r="I94" s="81"/>
+      <c r="J94" s="81"/>
+      <c r="K94" s="81"/>
+      <c r="L94" s="81"/>
+      <c r="M94" s="81"/>
+      <c r="N94" s="81"/>
+      <c r="O94" s="81"/>
+      <c r="P94" s="81"/>
+      <c r="Q94" s="81"/>
+      <c r="R94" s="81"/>
+      <c r="S94" s="81"/>
+      <c r="T94" s="81"/>
+      <c r="U94" s="81"/>
+      <c r="V94" s="81"/>
+      <c r="W94" s="81"/>
+      <c r="X94" s="81"/>
+      <c r="Y94" s="81"/>
     </row>
     <row r="95" spans="3:28">
-      <c r="D95" s="80"/>
-      <c r="E95" s="80"/>
-      <c r="F95" s="80"/>
-      <c r="G95" s="80"/>
-      <c r="H95" s="80"/>
-      <c r="I95" s="80"/>
-      <c r="J95" s="80"/>
-      <c r="K95" s="80"/>
-      <c r="L95" s="80"/>
-      <c r="M95" s="80"/>
-      <c r="N95" s="80"/>
-      <c r="O95" s="80"/>
-      <c r="P95" s="80"/>
-      <c r="Q95" s="80"/>
-      <c r="R95" s="80"/>
-      <c r="S95" s="80"/>
-      <c r="T95" s="80"/>
-      <c r="U95" s="80"/>
-      <c r="V95" s="80"/>
-      <c r="W95" s="80"/>
-      <c r="X95" s="80"/>
-      <c r="Y95" s="80"/>
+      <c r="D95" s="81"/>
+      <c r="E95" s="81"/>
+      <c r="F95" s="81"/>
+      <c r="G95" s="81"/>
+      <c r="H95" s="81"/>
+      <c r="I95" s="81"/>
+      <c r="J95" s="81"/>
+      <c r="K95" s="81"/>
+      <c r="L95" s="81"/>
+      <c r="M95" s="81"/>
+      <c r="N95" s="81"/>
+      <c r="O95" s="81"/>
+      <c r="P95" s="81"/>
+      <c r="Q95" s="81"/>
+      <c r="R95" s="81"/>
+      <c r="S95" s="81"/>
+      <c r="T95" s="81"/>
+      <c r="U95" s="81"/>
+      <c r="V95" s="81"/>
+      <c r="W95" s="81"/>
+      <c r="X95" s="81"/>
+      <c r="Y95" s="81"/>
     </row>
     <row r="96" spans="3:28">
-      <c r="D96" s="81" t="s">
+      <c r="D96" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="E96" s="81"/>
-      <c r="F96" s="81"/>
-      <c r="G96" s="81"/>
-      <c r="H96" s="81"/>
-      <c r="I96" s="81"/>
-      <c r="J96" s="81"/>
-      <c r="K96" s="81"/>
-      <c r="L96" s="81"/>
-      <c r="M96" s="81"/>
-      <c r="N96" s="81"/>
-      <c r="O96" s="81"/>
-      <c r="P96" s="81"/>
-      <c r="Q96" s="81"/>
-      <c r="R96" s="81"/>
-      <c r="S96" s="81"/>
-      <c r="T96" s="81"/>
-      <c r="U96" s="81"/>
-      <c r="V96" s="81"/>
-      <c r="W96" s="81"/>
-      <c r="X96" s="81"/>
-      <c r="Y96" s="81"/>
+      <c r="E96" s="80"/>
+      <c r="F96" s="80"/>
+      <c r="G96" s="80"/>
+      <c r="H96" s="80"/>
+      <c r="I96" s="80"/>
+      <c r="J96" s="80"/>
+      <c r="K96" s="80"/>
+      <c r="L96" s="80"/>
+      <c r="M96" s="80"/>
+      <c r="N96" s="80"/>
+      <c r="O96" s="80"/>
+      <c r="P96" s="80"/>
+      <c r="Q96" s="80"/>
+      <c r="R96" s="80"/>
+      <c r="S96" s="80"/>
+      <c r="T96" s="80"/>
+      <c r="U96" s="80"/>
+      <c r="V96" s="80"/>
+      <c r="W96" s="80"/>
+      <c r="X96" s="80"/>
+      <c r="Y96" s="80"/>
     </row>
     <row r="97" spans="2:48">
-      <c r="D97" s="81"/>
-      <c r="E97" s="81"/>
-      <c r="F97" s="81"/>
-      <c r="G97" s="81"/>
-      <c r="H97" s="81"/>
-      <c r="I97" s="81"/>
-      <c r="J97" s="81"/>
-      <c r="K97" s="81"/>
-      <c r="L97" s="81"/>
-      <c r="M97" s="81"/>
-      <c r="N97" s="81"/>
-      <c r="O97" s="81"/>
-      <c r="P97" s="81"/>
-      <c r="Q97" s="81"/>
-      <c r="R97" s="81"/>
-      <c r="S97" s="81"/>
-      <c r="T97" s="81"/>
-      <c r="U97" s="81"/>
-      <c r="V97" s="81"/>
-      <c r="W97" s="81"/>
-      <c r="X97" s="81"/>
-      <c r="Y97" s="81"/>
+      <c r="D97" s="80"/>
+      <c r="E97" s="80"/>
+      <c r="F97" s="80"/>
+      <c r="G97" s="80"/>
+      <c r="H97" s="80"/>
+      <c r="I97" s="80"/>
+      <c r="J97" s="80"/>
+      <c r="K97" s="80"/>
+      <c r="L97" s="80"/>
+      <c r="M97" s="80"/>
+      <c r="N97" s="80"/>
+      <c r="O97" s="80"/>
+      <c r="P97" s="80"/>
+      <c r="Q97" s="80"/>
+      <c r="R97" s="80"/>
+      <c r="S97" s="80"/>
+      <c r="T97" s="80"/>
+      <c r="U97" s="80"/>
+      <c r="V97" s="80"/>
+      <c r="W97" s="80"/>
+      <c r="X97" s="80"/>
+      <c r="Y97" s="80"/>
     </row>
     <row r="98" spans="2:48">
       <c r="B98" s="1" t="s">
@@ -11578,104 +11600,104 @@
       </c>
     </row>
     <row r="101" spans="2:48">
-      <c r="D101" s="80" t="s">
+      <c r="D101" s="81" t="s">
         <v>125</v>
       </c>
-      <c r="E101" s="80"/>
-      <c r="F101" s="80"/>
-      <c r="G101" s="80"/>
-      <c r="H101" s="80"/>
-      <c r="I101" s="80"/>
-      <c r="J101" s="80"/>
-      <c r="K101" s="80"/>
-      <c r="L101" s="80"/>
-      <c r="M101" s="80"/>
-      <c r="N101" s="80"/>
-      <c r="O101" s="80"/>
-      <c r="P101" s="80"/>
-      <c r="Q101" s="80"/>
-      <c r="R101" s="80"/>
-      <c r="S101" s="80"/>
-      <c r="T101" s="80"/>
-      <c r="U101" s="80"/>
-      <c r="V101" s="80"/>
-      <c r="W101" s="80"/>
-      <c r="X101" s="80"/>
-      <c r="Y101" s="80"/>
+      <c r="E101" s="81"/>
+      <c r="F101" s="81"/>
+      <c r="G101" s="81"/>
+      <c r="H101" s="81"/>
+      <c r="I101" s="81"/>
+      <c r="J101" s="81"/>
+      <c r="K101" s="81"/>
+      <c r="L101" s="81"/>
+      <c r="M101" s="81"/>
+      <c r="N101" s="81"/>
+      <c r="O101" s="81"/>
+      <c r="P101" s="81"/>
+      <c r="Q101" s="81"/>
+      <c r="R101" s="81"/>
+      <c r="S101" s="81"/>
+      <c r="T101" s="81"/>
+      <c r="U101" s="81"/>
+      <c r="V101" s="81"/>
+      <c r="W101" s="81"/>
+      <c r="X101" s="81"/>
+      <c r="Y101" s="81"/>
     </row>
     <row r="102" spans="2:48">
-      <c r="D102" s="80"/>
-      <c r="E102" s="80"/>
-      <c r="F102" s="80"/>
-      <c r="G102" s="80"/>
-      <c r="H102" s="80"/>
-      <c r="I102" s="80"/>
-      <c r="J102" s="80"/>
-      <c r="K102" s="80"/>
-      <c r="L102" s="80"/>
-      <c r="M102" s="80"/>
-      <c r="N102" s="80"/>
-      <c r="O102" s="80"/>
-      <c r="P102" s="80"/>
-      <c r="Q102" s="80"/>
-      <c r="R102" s="80"/>
-      <c r="S102" s="80"/>
-      <c r="T102" s="80"/>
-      <c r="U102" s="80"/>
-      <c r="V102" s="80"/>
-      <c r="W102" s="80"/>
-      <c r="X102" s="80"/>
-      <c r="Y102" s="80"/>
+      <c r="D102" s="81"/>
+      <c r="E102" s="81"/>
+      <c r="F102" s="81"/>
+      <c r="G102" s="81"/>
+      <c r="H102" s="81"/>
+      <c r="I102" s="81"/>
+      <c r="J102" s="81"/>
+      <c r="K102" s="81"/>
+      <c r="L102" s="81"/>
+      <c r="M102" s="81"/>
+      <c r="N102" s="81"/>
+      <c r="O102" s="81"/>
+      <c r="P102" s="81"/>
+      <c r="Q102" s="81"/>
+      <c r="R102" s="81"/>
+      <c r="S102" s="81"/>
+      <c r="T102" s="81"/>
+      <c r="U102" s="81"/>
+      <c r="V102" s="81"/>
+      <c r="W102" s="81"/>
+      <c r="X102" s="81"/>
+      <c r="Y102" s="81"/>
     </row>
     <row r="103" spans="2:48">
-      <c r="D103" s="81" t="s">
+      <c r="D103" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="E103" s="81"/>
-      <c r="F103" s="81"/>
-      <c r="G103" s="81"/>
-      <c r="H103" s="81"/>
-      <c r="I103" s="81"/>
-      <c r="J103" s="81"/>
-      <c r="K103" s="81"/>
-      <c r="L103" s="81"/>
-      <c r="M103" s="81"/>
-      <c r="N103" s="81"/>
-      <c r="O103" s="81"/>
-      <c r="P103" s="81"/>
-      <c r="Q103" s="81"/>
-      <c r="R103" s="81"/>
-      <c r="S103" s="81"/>
-      <c r="T103" s="81"/>
-      <c r="U103" s="81"/>
-      <c r="V103" s="81"/>
-      <c r="W103" s="81"/>
-      <c r="X103" s="81"/>
-      <c r="Y103" s="81"/>
+      <c r="E103" s="80"/>
+      <c r="F103" s="80"/>
+      <c r="G103" s="80"/>
+      <c r="H103" s="80"/>
+      <c r="I103" s="80"/>
+      <c r="J103" s="80"/>
+      <c r="K103" s="80"/>
+      <c r="L103" s="80"/>
+      <c r="M103" s="80"/>
+      <c r="N103" s="80"/>
+      <c r="O103" s="80"/>
+      <c r="P103" s="80"/>
+      <c r="Q103" s="80"/>
+      <c r="R103" s="80"/>
+      <c r="S103" s="80"/>
+      <c r="T103" s="80"/>
+      <c r="U103" s="80"/>
+      <c r="V103" s="80"/>
+      <c r="W103" s="80"/>
+      <c r="X103" s="80"/>
+      <c r="Y103" s="80"/>
     </row>
     <row r="104" spans="2:48">
-      <c r="D104" s="81"/>
-      <c r="E104" s="81"/>
-      <c r="F104" s="81"/>
-      <c r="G104" s="81"/>
-      <c r="H104" s="81"/>
-      <c r="I104" s="81"/>
-      <c r="J104" s="81"/>
-      <c r="K104" s="81"/>
-      <c r="L104" s="81"/>
-      <c r="M104" s="81"/>
-      <c r="N104" s="81"/>
-      <c r="O104" s="81"/>
-      <c r="P104" s="81"/>
-      <c r="Q104" s="81"/>
-      <c r="R104" s="81"/>
-      <c r="S104" s="81"/>
-      <c r="T104" s="81"/>
-      <c r="U104" s="81"/>
-      <c r="V104" s="81"/>
-      <c r="W104" s="81"/>
-      <c r="X104" s="81"/>
-      <c r="Y104" s="81"/>
+      <c r="D104" s="80"/>
+      <c r="E104" s="80"/>
+      <c r="F104" s="80"/>
+      <c r="G104" s="80"/>
+      <c r="H104" s="80"/>
+      <c r="I104" s="80"/>
+      <c r="J104" s="80"/>
+      <c r="K104" s="80"/>
+      <c r="L104" s="80"/>
+      <c r="M104" s="80"/>
+      <c r="N104" s="80"/>
+      <c r="O104" s="80"/>
+      <c r="P104" s="80"/>
+      <c r="Q104" s="80"/>
+      <c r="R104" s="80"/>
+      <c r="S104" s="80"/>
+      <c r="T104" s="80"/>
+      <c r="U104" s="80"/>
+      <c r="V104" s="80"/>
+      <c r="W104" s="80"/>
+      <c r="X104" s="80"/>
+      <c r="Y104" s="80"/>
     </row>
     <row r="105" spans="2:48">
       <c r="B105" s="1" t="s">
@@ -11696,101 +11718,101 @@
       <c r="C108" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D108" s="81" t="s">
+      <c r="D108" s="80" t="s">
         <v>130</v>
       </c>
-      <c r="E108" s="81"/>
-      <c r="F108" s="81"/>
-      <c r="G108" s="81"/>
-      <c r="H108" s="81"/>
-      <c r="I108" s="81"/>
-      <c r="J108" s="81"/>
-      <c r="K108" s="81"/>
-      <c r="L108" s="81"/>
-      <c r="M108" s="81"/>
-      <c r="N108" s="81"/>
-      <c r="O108" s="81"/>
-      <c r="P108" s="81"/>
-      <c r="Q108" s="81"/>
-      <c r="R108" s="81"/>
-      <c r="S108" s="81"/>
-      <c r="T108" s="81"/>
-      <c r="U108" s="81"/>
-      <c r="V108" s="81"/>
-      <c r="W108" s="81"/>
-      <c r="X108" s="81"/>
-      <c r="Y108" s="81"/>
-      <c r="Z108" s="81"/>
-      <c r="AA108" s="81"/>
-      <c r="AB108" s="81"/>
-      <c r="AC108" s="81"/>
-      <c r="AD108" s="81"/>
-      <c r="AE108" s="81"/>
-      <c r="AF108" s="81"/>
-      <c r="AG108" s="81"/>
-      <c r="AH108" s="81"/>
-      <c r="AI108" s="81"/>
-      <c r="AJ108" s="81"/>
-      <c r="AK108" s="81"/>
-      <c r="AL108" s="81"/>
-      <c r="AM108" s="81"/>
-      <c r="AN108" s="81"/>
-      <c r="AO108" s="81"/>
-      <c r="AP108" s="81"/>
-      <c r="AQ108" s="81"/>
-      <c r="AR108" s="81"/>
-      <c r="AS108" s="81"/>
-      <c r="AT108" s="81"/>
-      <c r="AU108" s="81"/>
-      <c r="AV108" s="81"/>
+      <c r="E108" s="80"/>
+      <c r="F108" s="80"/>
+      <c r="G108" s="80"/>
+      <c r="H108" s="80"/>
+      <c r="I108" s="80"/>
+      <c r="J108" s="80"/>
+      <c r="K108" s="80"/>
+      <c r="L108" s="80"/>
+      <c r="M108" s="80"/>
+      <c r="N108" s="80"/>
+      <c r="O108" s="80"/>
+      <c r="P108" s="80"/>
+      <c r="Q108" s="80"/>
+      <c r="R108" s="80"/>
+      <c r="S108" s="80"/>
+      <c r="T108" s="80"/>
+      <c r="U108" s="80"/>
+      <c r="V108" s="80"/>
+      <c r="W108" s="80"/>
+      <c r="X108" s="80"/>
+      <c r="Y108" s="80"/>
+      <c r="Z108" s="80"/>
+      <c r="AA108" s="80"/>
+      <c r="AB108" s="80"/>
+      <c r="AC108" s="80"/>
+      <c r="AD108" s="80"/>
+      <c r="AE108" s="80"/>
+      <c r="AF108" s="80"/>
+      <c r="AG108" s="80"/>
+      <c r="AH108" s="80"/>
+      <c r="AI108" s="80"/>
+      <c r="AJ108" s="80"/>
+      <c r="AK108" s="80"/>
+      <c r="AL108" s="80"/>
+      <c r="AM108" s="80"/>
+      <c r="AN108" s="80"/>
+      <c r="AO108" s="80"/>
+      <c r="AP108" s="80"/>
+      <c r="AQ108" s="80"/>
+      <c r="AR108" s="80"/>
+      <c r="AS108" s="80"/>
+      <c r="AT108" s="80"/>
+      <c r="AU108" s="80"/>
+      <c r="AV108" s="80"/>
     </row>
     <row r="109" spans="2:48">
       <c r="C109" s="56"/>
-      <c r="D109" s="81"/>
-      <c r="E109" s="81"/>
-      <c r="F109" s="81"/>
-      <c r="G109" s="81"/>
-      <c r="H109" s="81"/>
-      <c r="I109" s="81"/>
-      <c r="J109" s="81"/>
-      <c r="K109" s="81"/>
-      <c r="L109" s="81"/>
-      <c r="M109" s="81"/>
-      <c r="N109" s="81"/>
-      <c r="O109" s="81"/>
-      <c r="P109" s="81"/>
-      <c r="Q109" s="81"/>
-      <c r="R109" s="81"/>
-      <c r="S109" s="81"/>
-      <c r="T109" s="81"/>
-      <c r="U109" s="81"/>
-      <c r="V109" s="81"/>
-      <c r="W109" s="81"/>
-      <c r="X109" s="81"/>
-      <c r="Y109" s="81"/>
-      <c r="Z109" s="81"/>
-      <c r="AA109" s="81"/>
-      <c r="AB109" s="81"/>
-      <c r="AC109" s="81"/>
-      <c r="AD109" s="81"/>
-      <c r="AE109" s="81"/>
-      <c r="AF109" s="81"/>
-      <c r="AG109" s="81"/>
-      <c r="AH109" s="81"/>
-      <c r="AI109" s="81"/>
-      <c r="AJ109" s="81"/>
-      <c r="AK109" s="81"/>
-      <c r="AL109" s="81"/>
-      <c r="AM109" s="81"/>
-      <c r="AN109" s="81"/>
-      <c r="AO109" s="81"/>
-      <c r="AP109" s="81"/>
-      <c r="AQ109" s="81"/>
-      <c r="AR109" s="81"/>
-      <c r="AS109" s="81"/>
-      <c r="AT109" s="81"/>
-      <c r="AU109" s="81"/>
-      <c r="AV109" s="81"/>
+      <c r="D109" s="80"/>
+      <c r="E109" s="80"/>
+      <c r="F109" s="80"/>
+      <c r="G109" s="80"/>
+      <c r="H109" s="80"/>
+      <c r="I109" s="80"/>
+      <c r="J109" s="80"/>
+      <c r="K109" s="80"/>
+      <c r="L109" s="80"/>
+      <c r="M109" s="80"/>
+      <c r="N109" s="80"/>
+      <c r="O109" s="80"/>
+      <c r="P109" s="80"/>
+      <c r="Q109" s="80"/>
+      <c r="R109" s="80"/>
+      <c r="S109" s="80"/>
+      <c r="T109" s="80"/>
+      <c r="U109" s="80"/>
+      <c r="V109" s="80"/>
+      <c r="W109" s="80"/>
+      <c r="X109" s="80"/>
+      <c r="Y109" s="80"/>
+      <c r="Z109" s="80"/>
+      <c r="AA109" s="80"/>
+      <c r="AB109" s="80"/>
+      <c r="AC109" s="80"/>
+      <c r="AD109" s="80"/>
+      <c r="AE109" s="80"/>
+      <c r="AF109" s="80"/>
+      <c r="AG109" s="80"/>
+      <c r="AH109" s="80"/>
+      <c r="AI109" s="80"/>
+      <c r="AJ109" s="80"/>
+      <c r="AK109" s="80"/>
+      <c r="AL109" s="80"/>
+      <c r="AM109" s="80"/>
+      <c r="AN109" s="80"/>
+      <c r="AO109" s="80"/>
+      <c r="AP109" s="80"/>
+      <c r="AQ109" s="80"/>
+      <c r="AR109" s="80"/>
+      <c r="AS109" s="80"/>
+      <c r="AT109" s="80"/>
+      <c r="AU109" s="80"/>
+      <c r="AV109" s="80"/>
     </row>
     <row r="110" spans="2:48">
       <c r="C110" s="29" t="s">
@@ -11855,207 +11877,207 @@
       <c r="C117" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D117" s="80" t="s">
+      <c r="D117" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="E117" s="80"/>
-      <c r="F117" s="80"/>
-      <c r="G117" s="80"/>
-      <c r="H117" s="80"/>
-      <c r="I117" s="80"/>
-      <c r="J117" s="80"/>
-      <c r="K117" s="80"/>
-      <c r="L117" s="80"/>
-      <c r="M117" s="80"/>
-      <c r="N117" s="80"/>
-      <c r="O117" s="80"/>
-      <c r="P117" s="80"/>
-      <c r="Q117" s="80"/>
-      <c r="R117" s="80"/>
-      <c r="S117" s="80"/>
-      <c r="T117" s="80"/>
-      <c r="U117" s="80"/>
-      <c r="V117" s="80"/>
-      <c r="W117" s="80"/>
-      <c r="X117" s="80"/>
-      <c r="Y117" s="80"/>
+      <c r="E117" s="81"/>
+      <c r="F117" s="81"/>
+      <c r="G117" s="81"/>
+      <c r="H117" s="81"/>
+      <c r="I117" s="81"/>
+      <c r="J117" s="81"/>
+      <c r="K117" s="81"/>
+      <c r="L117" s="81"/>
+      <c r="M117" s="81"/>
+      <c r="N117" s="81"/>
+      <c r="O117" s="81"/>
+      <c r="P117" s="81"/>
+      <c r="Q117" s="81"/>
+      <c r="R117" s="81"/>
+      <c r="S117" s="81"/>
+      <c r="T117" s="81"/>
+      <c r="U117" s="81"/>
+      <c r="V117" s="81"/>
+      <c r="W117" s="81"/>
+      <c r="X117" s="81"/>
+      <c r="Y117" s="81"/>
     </row>
     <row r="118" spans="3:27">
-      <c r="D118" s="80"/>
-      <c r="E118" s="80"/>
-      <c r="F118" s="80"/>
-      <c r="G118" s="80"/>
-      <c r="H118" s="80"/>
-      <c r="I118" s="80"/>
-      <c r="J118" s="80"/>
-      <c r="K118" s="80"/>
-      <c r="L118" s="80"/>
-      <c r="M118" s="80"/>
-      <c r="N118" s="80"/>
-      <c r="O118" s="80"/>
-      <c r="P118" s="80"/>
-      <c r="Q118" s="80"/>
-      <c r="R118" s="80"/>
-      <c r="S118" s="80"/>
-      <c r="T118" s="80"/>
-      <c r="U118" s="80"/>
-      <c r="V118" s="80"/>
-      <c r="W118" s="80"/>
-      <c r="X118" s="80"/>
-      <c r="Y118" s="80"/>
+      <c r="D118" s="81"/>
+      <c r="E118" s="81"/>
+      <c r="F118" s="81"/>
+      <c r="G118" s="81"/>
+      <c r="H118" s="81"/>
+      <c r="I118" s="81"/>
+      <c r="J118" s="81"/>
+      <c r="K118" s="81"/>
+      <c r="L118" s="81"/>
+      <c r="M118" s="81"/>
+      <c r="N118" s="81"/>
+      <c r="O118" s="81"/>
+      <c r="P118" s="81"/>
+      <c r="Q118" s="81"/>
+      <c r="R118" s="81"/>
+      <c r="S118" s="81"/>
+      <c r="T118" s="81"/>
+      <c r="U118" s="81"/>
+      <c r="V118" s="81"/>
+      <c r="W118" s="81"/>
+      <c r="X118" s="81"/>
+      <c r="Y118" s="81"/>
     </row>
     <row r="119" spans="3:27">
-      <c r="D119" s="80"/>
-      <c r="E119" s="80"/>
-      <c r="F119" s="80"/>
-      <c r="G119" s="80"/>
-      <c r="H119" s="80"/>
-      <c r="I119" s="80"/>
-      <c r="J119" s="80"/>
-      <c r="K119" s="80"/>
-      <c r="L119" s="80"/>
-      <c r="M119" s="80"/>
-      <c r="N119" s="80"/>
-      <c r="O119" s="80"/>
-      <c r="P119" s="80"/>
-      <c r="Q119" s="80"/>
-      <c r="R119" s="80"/>
-      <c r="S119" s="80"/>
-      <c r="T119" s="80"/>
-      <c r="U119" s="80"/>
-      <c r="V119" s="80"/>
-      <c r="W119" s="80"/>
-      <c r="X119" s="80"/>
-      <c r="Y119" s="80"/>
+      <c r="D119" s="81"/>
+      <c r="E119" s="81"/>
+      <c r="F119" s="81"/>
+      <c r="G119" s="81"/>
+      <c r="H119" s="81"/>
+      <c r="I119" s="81"/>
+      <c r="J119" s="81"/>
+      <c r="K119" s="81"/>
+      <c r="L119" s="81"/>
+      <c r="M119" s="81"/>
+      <c r="N119" s="81"/>
+      <c r="O119" s="81"/>
+      <c r="P119" s="81"/>
+      <c r="Q119" s="81"/>
+      <c r="R119" s="81"/>
+      <c r="S119" s="81"/>
+      <c r="T119" s="81"/>
+      <c r="U119" s="81"/>
+      <c r="V119" s="81"/>
+      <c r="W119" s="81"/>
+      <c r="X119" s="81"/>
+      <c r="Y119" s="81"/>
     </row>
     <row r="120" spans="3:27">
-      <c r="D120" s="80"/>
-      <c r="E120" s="80"/>
-      <c r="F120" s="80"/>
-      <c r="G120" s="80"/>
-      <c r="H120" s="80"/>
-      <c r="I120" s="80"/>
-      <c r="J120" s="80"/>
-      <c r="K120" s="80"/>
-      <c r="L120" s="80"/>
-      <c r="M120" s="80"/>
-      <c r="N120" s="80"/>
-      <c r="O120" s="80"/>
-      <c r="P120" s="80"/>
-      <c r="Q120" s="80"/>
-      <c r="R120" s="80"/>
-      <c r="S120" s="80"/>
-      <c r="T120" s="80"/>
-      <c r="U120" s="80"/>
-      <c r="V120" s="80"/>
-      <c r="W120" s="80"/>
-      <c r="X120" s="80"/>
-      <c r="Y120" s="80"/>
+      <c r="D120" s="81"/>
+      <c r="E120" s="81"/>
+      <c r="F120" s="81"/>
+      <c r="G120" s="81"/>
+      <c r="H120" s="81"/>
+      <c r="I120" s="81"/>
+      <c r="J120" s="81"/>
+      <c r="K120" s="81"/>
+      <c r="L120" s="81"/>
+      <c r="M120" s="81"/>
+      <c r="N120" s="81"/>
+      <c r="O120" s="81"/>
+      <c r="P120" s="81"/>
+      <c r="Q120" s="81"/>
+      <c r="R120" s="81"/>
+      <c r="S120" s="81"/>
+      <c r="T120" s="81"/>
+      <c r="U120" s="81"/>
+      <c r="V120" s="81"/>
+      <c r="W120" s="81"/>
+      <c r="X120" s="81"/>
+      <c r="Y120" s="81"/>
     </row>
     <row r="121" spans="3:27">
       <c r="C121" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D121" s="80" t="s">
+      <c r="D121" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="E121" s="80"/>
-      <c r="F121" s="80"/>
-      <c r="G121" s="80"/>
-      <c r="H121" s="80"/>
-      <c r="I121" s="80"/>
-      <c r="J121" s="80"/>
-      <c r="K121" s="80"/>
-      <c r="L121" s="80"/>
-      <c r="M121" s="80"/>
-      <c r="N121" s="80"/>
-      <c r="O121" s="80"/>
-      <c r="P121" s="80"/>
-      <c r="Q121" s="80"/>
-      <c r="R121" s="80"/>
-      <c r="S121" s="80"/>
-      <c r="T121" s="80"/>
-      <c r="U121" s="80"/>
-      <c r="V121" s="80"/>
-      <c r="W121" s="80"/>
-      <c r="X121" s="80"/>
-      <c r="Y121" s="80"/>
+      <c r="E121" s="81"/>
+      <c r="F121" s="81"/>
+      <c r="G121" s="81"/>
+      <c r="H121" s="81"/>
+      <c r="I121" s="81"/>
+      <c r="J121" s="81"/>
+      <c r="K121" s="81"/>
+      <c r="L121" s="81"/>
+      <c r="M121" s="81"/>
+      <c r="N121" s="81"/>
+      <c r="O121" s="81"/>
+      <c r="P121" s="81"/>
+      <c r="Q121" s="81"/>
+      <c r="R121" s="81"/>
+      <c r="S121" s="81"/>
+      <c r="T121" s="81"/>
+      <c r="U121" s="81"/>
+      <c r="V121" s="81"/>
+      <c r="W121" s="81"/>
+      <c r="X121" s="81"/>
+      <c r="Y121" s="81"/>
     </row>
     <row r="122" spans="3:27">
-      <c r="D122" s="80"/>
-      <c r="E122" s="80"/>
-      <c r="F122" s="80"/>
-      <c r="G122" s="80"/>
-      <c r="H122" s="80"/>
-      <c r="I122" s="80"/>
-      <c r="J122" s="80"/>
-      <c r="K122" s="80"/>
-      <c r="L122" s="80"/>
-      <c r="M122" s="80"/>
-      <c r="N122" s="80"/>
-      <c r="O122" s="80"/>
-      <c r="P122" s="80"/>
-      <c r="Q122" s="80"/>
-      <c r="R122" s="80"/>
-      <c r="S122" s="80"/>
-      <c r="T122" s="80"/>
-      <c r="U122" s="80"/>
-      <c r="V122" s="80"/>
-      <c r="W122" s="80"/>
-      <c r="X122" s="80"/>
-      <c r="Y122" s="80"/>
+      <c r="D122" s="81"/>
+      <c r="E122" s="81"/>
+      <c r="F122" s="81"/>
+      <c r="G122" s="81"/>
+      <c r="H122" s="81"/>
+      <c r="I122" s="81"/>
+      <c r="J122" s="81"/>
+      <c r="K122" s="81"/>
+      <c r="L122" s="81"/>
+      <c r="M122" s="81"/>
+      <c r="N122" s="81"/>
+      <c r="O122" s="81"/>
+      <c r="P122" s="81"/>
+      <c r="Q122" s="81"/>
+      <c r="R122" s="81"/>
+      <c r="S122" s="81"/>
+      <c r="T122" s="81"/>
+      <c r="U122" s="81"/>
+      <c r="V122" s="81"/>
+      <c r="W122" s="81"/>
+      <c r="X122" s="81"/>
+      <c r="Y122" s="81"/>
     </row>
     <row r="123" spans="3:27" ht="14.25" customHeight="1">
-      <c r="D123" s="81" t="s">
+      <c r="D123" s="80" t="s">
         <v>140</v>
       </c>
-      <c r="E123" s="81"/>
-      <c r="F123" s="81"/>
-      <c r="G123" s="81"/>
-      <c r="H123" s="81"/>
-      <c r="I123" s="81"/>
-      <c r="J123" s="81"/>
-      <c r="K123" s="81"/>
-      <c r="L123" s="81"/>
-      <c r="M123" s="81"/>
-      <c r="N123" s="81"/>
-      <c r="O123" s="81"/>
-      <c r="P123" s="81"/>
-      <c r="Q123" s="81"/>
-      <c r="R123" s="81"/>
-      <c r="S123" s="81"/>
-      <c r="T123" s="81"/>
-      <c r="U123" s="81"/>
-      <c r="V123" s="81"/>
-      <c r="W123" s="81"/>
-      <c r="X123" s="81"/>
-      <c r="Y123" s="81"/>
-      <c r="Z123" s="81"/>
+      <c r="E123" s="80"/>
+      <c r="F123" s="80"/>
+      <c r="G123" s="80"/>
+      <c r="H123" s="80"/>
+      <c r="I123" s="80"/>
+      <c r="J123" s="80"/>
+      <c r="K123" s="80"/>
+      <c r="L123" s="80"/>
+      <c r="M123" s="80"/>
+      <c r="N123" s="80"/>
+      <c r="O123" s="80"/>
+      <c r="P123" s="80"/>
+      <c r="Q123" s="80"/>
+      <c r="R123" s="80"/>
+      <c r="S123" s="80"/>
+      <c r="T123" s="80"/>
+      <c r="U123" s="80"/>
+      <c r="V123" s="80"/>
+      <c r="W123" s="80"/>
+      <c r="X123" s="80"/>
+      <c r="Y123" s="80"/>
+      <c r="Z123" s="80"/>
     </row>
     <row r="124" spans="3:27">
-      <c r="D124" s="81"/>
-      <c r="E124" s="81"/>
-      <c r="F124" s="81"/>
-      <c r="G124" s="81"/>
-      <c r="H124" s="81"/>
-      <c r="I124" s="81"/>
-      <c r="J124" s="81"/>
-      <c r="K124" s="81"/>
-      <c r="L124" s="81"/>
-      <c r="M124" s="81"/>
-      <c r="N124" s="81"/>
-      <c r="O124" s="81"/>
-      <c r="P124" s="81"/>
-      <c r="Q124" s="81"/>
-      <c r="R124" s="81"/>
-      <c r="S124" s="81"/>
-      <c r="T124" s="81"/>
-      <c r="U124" s="81"/>
-      <c r="V124" s="81"/>
-      <c r="W124" s="81"/>
-      <c r="X124" s="81"/>
-      <c r="Y124" s="81"/>
-      <c r="Z124" s="81"/>
+      <c r="D124" s="80"/>
+      <c r="E124" s="80"/>
+      <c r="F124" s="80"/>
+      <c r="G124" s="80"/>
+      <c r="H124" s="80"/>
+      <c r="I124" s="80"/>
+      <c r="J124" s="80"/>
+      <c r="K124" s="80"/>
+      <c r="L124" s="80"/>
+      <c r="M124" s="80"/>
+      <c r="N124" s="80"/>
+      <c r="O124" s="80"/>
+      <c r="P124" s="80"/>
+      <c r="Q124" s="80"/>
+      <c r="R124" s="80"/>
+      <c r="S124" s="80"/>
+      <c r="T124" s="80"/>
+      <c r="U124" s="80"/>
+      <c r="V124" s="80"/>
+      <c r="W124" s="80"/>
+      <c r="X124" s="80"/>
+      <c r="Y124" s="80"/>
+      <c r="Z124" s="80"/>
     </row>
     <row r="125" spans="3:27" ht="14.25" customHeight="1">
       <c r="C125" s="29" t="s">
@@ -12144,54 +12166,54 @@
       <c r="C128" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D128" s="81" t="s">
+      <c r="D128" s="80" t="s">
         <v>142</v>
       </c>
-      <c r="E128" s="81"/>
-      <c r="F128" s="81"/>
-      <c r="G128" s="81"/>
-      <c r="H128" s="81"/>
-      <c r="I128" s="81"/>
-      <c r="J128" s="81"/>
-      <c r="K128" s="81"/>
-      <c r="L128" s="81"/>
-      <c r="M128" s="81"/>
-      <c r="N128" s="81"/>
-      <c r="O128" s="81"/>
-      <c r="P128" s="81"/>
-      <c r="Q128" s="81"/>
-      <c r="R128" s="81"/>
-      <c r="S128" s="81"/>
-      <c r="T128" s="81"/>
-      <c r="U128" s="81"/>
-      <c r="V128" s="81"/>
-      <c r="W128" s="81"/>
-      <c r="X128" s="81"/>
-      <c r="Y128" s="81"/>
+      <c r="E128" s="80"/>
+      <c r="F128" s="80"/>
+      <c r="G128" s="80"/>
+      <c r="H128" s="80"/>
+      <c r="I128" s="80"/>
+      <c r="J128" s="80"/>
+      <c r="K128" s="80"/>
+      <c r="L128" s="80"/>
+      <c r="M128" s="80"/>
+      <c r="N128" s="80"/>
+      <c r="O128" s="80"/>
+      <c r="P128" s="80"/>
+      <c r="Q128" s="80"/>
+      <c r="R128" s="80"/>
+      <c r="S128" s="80"/>
+      <c r="T128" s="80"/>
+      <c r="U128" s="80"/>
+      <c r="V128" s="80"/>
+      <c r="W128" s="80"/>
+      <c r="X128" s="80"/>
+      <c r="Y128" s="80"/>
     </row>
     <row r="129" spans="2:25">
-      <c r="D129" s="81"/>
-      <c r="E129" s="81"/>
-      <c r="F129" s="81"/>
-      <c r="G129" s="81"/>
-      <c r="H129" s="81"/>
-      <c r="I129" s="81"/>
-      <c r="J129" s="81"/>
-      <c r="K129" s="81"/>
-      <c r="L129" s="81"/>
-      <c r="M129" s="81"/>
-      <c r="N129" s="81"/>
-      <c r="O129" s="81"/>
-      <c r="P129" s="81"/>
-      <c r="Q129" s="81"/>
-      <c r="R129" s="81"/>
-      <c r="S129" s="81"/>
-      <c r="T129" s="81"/>
-      <c r="U129" s="81"/>
-      <c r="V129" s="81"/>
-      <c r="W129" s="81"/>
-      <c r="X129" s="81"/>
-      <c r="Y129" s="81"/>
+      <c r="D129" s="80"/>
+      <c r="E129" s="80"/>
+      <c r="F129" s="80"/>
+      <c r="G129" s="80"/>
+      <c r="H129" s="80"/>
+      <c r="I129" s="80"/>
+      <c r="J129" s="80"/>
+      <c r="K129" s="80"/>
+      <c r="L129" s="80"/>
+      <c r="M129" s="80"/>
+      <c r="N129" s="80"/>
+      <c r="O129" s="80"/>
+      <c r="P129" s="80"/>
+      <c r="Q129" s="80"/>
+      <c r="R129" s="80"/>
+      <c r="S129" s="80"/>
+      <c r="T129" s="80"/>
+      <c r="U129" s="80"/>
+      <c r="V129" s="80"/>
+      <c r="W129" s="80"/>
+      <c r="X129" s="80"/>
+      <c r="Y129" s="80"/>
     </row>
     <row r="130" spans="2:25">
       <c r="C130" s="29" t="s">
@@ -12210,78 +12232,78 @@
       <c r="C132" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D132" s="80" t="s">
+      <c r="D132" s="81" t="s">
         <v>145</v>
       </c>
-      <c r="E132" s="80"/>
-      <c r="F132" s="80"/>
-      <c r="G132" s="80"/>
-      <c r="H132" s="80"/>
-      <c r="I132" s="80"/>
-      <c r="J132" s="80"/>
-      <c r="K132" s="80"/>
-      <c r="L132" s="80"/>
-      <c r="M132" s="80"/>
-      <c r="N132" s="80"/>
-      <c r="O132" s="80"/>
-      <c r="P132" s="80"/>
-      <c r="Q132" s="80"/>
-      <c r="R132" s="80"/>
-      <c r="S132" s="80"/>
-      <c r="T132" s="80"/>
-      <c r="U132" s="80"/>
-      <c r="V132" s="80"/>
-      <c r="W132" s="80"/>
-      <c r="X132" s="80"/>
-      <c r="Y132" s="80"/>
+      <c r="E132" s="81"/>
+      <c r="F132" s="81"/>
+      <c r="G132" s="81"/>
+      <c r="H132" s="81"/>
+      <c r="I132" s="81"/>
+      <c r="J132" s="81"/>
+      <c r="K132" s="81"/>
+      <c r="L132" s="81"/>
+      <c r="M132" s="81"/>
+      <c r="N132" s="81"/>
+      <c r="O132" s="81"/>
+      <c r="P132" s="81"/>
+      <c r="Q132" s="81"/>
+      <c r="R132" s="81"/>
+      <c r="S132" s="81"/>
+      <c r="T132" s="81"/>
+      <c r="U132" s="81"/>
+      <c r="V132" s="81"/>
+      <c r="W132" s="81"/>
+      <c r="X132" s="81"/>
+      <c r="Y132" s="81"/>
     </row>
     <row r="133" spans="2:25">
-      <c r="D133" s="80"/>
-      <c r="E133" s="80"/>
-      <c r="F133" s="80"/>
-      <c r="G133" s="80"/>
-      <c r="H133" s="80"/>
-      <c r="I133" s="80"/>
-      <c r="J133" s="80"/>
-      <c r="K133" s="80"/>
-      <c r="L133" s="80"/>
-      <c r="M133" s="80"/>
-      <c r="N133" s="80"/>
-      <c r="O133" s="80"/>
-      <c r="P133" s="80"/>
-      <c r="Q133" s="80"/>
-      <c r="R133" s="80"/>
-      <c r="S133" s="80"/>
-      <c r="T133" s="80"/>
-      <c r="U133" s="80"/>
-      <c r="V133" s="80"/>
-      <c r="W133" s="80"/>
-      <c r="X133" s="80"/>
-      <c r="Y133" s="80"/>
+      <c r="D133" s="81"/>
+      <c r="E133" s="81"/>
+      <c r="F133" s="81"/>
+      <c r="G133" s="81"/>
+      <c r="H133" s="81"/>
+      <c r="I133" s="81"/>
+      <c r="J133" s="81"/>
+      <c r="K133" s="81"/>
+      <c r="L133" s="81"/>
+      <c r="M133" s="81"/>
+      <c r="N133" s="81"/>
+      <c r="O133" s="81"/>
+      <c r="P133" s="81"/>
+      <c r="Q133" s="81"/>
+      <c r="R133" s="81"/>
+      <c r="S133" s="81"/>
+      <c r="T133" s="81"/>
+      <c r="U133" s="81"/>
+      <c r="V133" s="81"/>
+      <c r="W133" s="81"/>
+      <c r="X133" s="81"/>
+      <c r="Y133" s="81"/>
     </row>
     <row r="134" spans="2:25">
-      <c r="D134" s="80"/>
-      <c r="E134" s="80"/>
-      <c r="F134" s="80"/>
-      <c r="G134" s="80"/>
-      <c r="H134" s="80"/>
-      <c r="I134" s="80"/>
-      <c r="J134" s="80"/>
-      <c r="K134" s="80"/>
-      <c r="L134" s="80"/>
-      <c r="M134" s="80"/>
-      <c r="N134" s="80"/>
-      <c r="O134" s="80"/>
-      <c r="P134" s="80"/>
-      <c r="Q134" s="80"/>
-      <c r="R134" s="80"/>
-      <c r="S134" s="80"/>
-      <c r="T134" s="80"/>
-      <c r="U134" s="80"/>
-      <c r="V134" s="80"/>
-      <c r="W134" s="80"/>
-      <c r="X134" s="80"/>
-      <c r="Y134" s="80"/>
+      <c r="D134" s="81"/>
+      <c r="E134" s="81"/>
+      <c r="F134" s="81"/>
+      <c r="G134" s="81"/>
+      <c r="H134" s="81"/>
+      <c r="I134" s="81"/>
+      <c r="J134" s="81"/>
+      <c r="K134" s="81"/>
+      <c r="L134" s="81"/>
+      <c r="M134" s="81"/>
+      <c r="N134" s="81"/>
+      <c r="O134" s="81"/>
+      <c r="P134" s="81"/>
+      <c r="Q134" s="81"/>
+      <c r="R134" s="81"/>
+      <c r="S134" s="81"/>
+      <c r="T134" s="81"/>
+      <c r="U134" s="81"/>
+      <c r="V134" s="81"/>
+      <c r="W134" s="81"/>
+      <c r="X134" s="81"/>
+      <c r="Y134" s="81"/>
     </row>
     <row r="135" spans="2:25">
       <c r="C135" s="29" t="s">
@@ -12295,102 +12317,102 @@
       <c r="C136" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D136" s="81" t="s">
+      <c r="D136" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="E136" s="81"/>
-      <c r="F136" s="81"/>
-      <c r="G136" s="81"/>
-      <c r="H136" s="81"/>
-      <c r="I136" s="81"/>
-      <c r="J136" s="81"/>
-      <c r="K136" s="81"/>
-      <c r="L136" s="81"/>
-      <c r="M136" s="81"/>
-      <c r="N136" s="81"/>
-      <c r="O136" s="81"/>
-      <c r="P136" s="81"/>
-      <c r="Q136" s="81"/>
-      <c r="R136" s="81"/>
-      <c r="S136" s="81"/>
-      <c r="T136" s="81"/>
-      <c r="U136" s="81"/>
-      <c r="V136" s="81"/>
-      <c r="W136" s="81"/>
-      <c r="X136" s="81"/>
-      <c r="Y136" s="81"/>
+      <c r="E136" s="80"/>
+      <c r="F136" s="80"/>
+      <c r="G136" s="80"/>
+      <c r="H136" s="80"/>
+      <c r="I136" s="80"/>
+      <c r="J136" s="80"/>
+      <c r="K136" s="80"/>
+      <c r="L136" s="80"/>
+      <c r="M136" s="80"/>
+      <c r="N136" s="80"/>
+      <c r="O136" s="80"/>
+      <c r="P136" s="80"/>
+      <c r="Q136" s="80"/>
+      <c r="R136" s="80"/>
+      <c r="S136" s="80"/>
+      <c r="T136" s="80"/>
+      <c r="U136" s="80"/>
+      <c r="V136" s="80"/>
+      <c r="W136" s="80"/>
+      <c r="X136" s="80"/>
+      <c r="Y136" s="80"/>
     </row>
     <row r="137" spans="2:25">
-      <c r="D137" s="81"/>
-      <c r="E137" s="81"/>
-      <c r="F137" s="81"/>
-      <c r="G137" s="81"/>
-      <c r="H137" s="81"/>
-      <c r="I137" s="81"/>
-      <c r="J137" s="81"/>
-      <c r="K137" s="81"/>
-      <c r="L137" s="81"/>
-      <c r="M137" s="81"/>
-      <c r="N137" s="81"/>
-      <c r="O137" s="81"/>
-      <c r="P137" s="81"/>
-      <c r="Q137" s="81"/>
-      <c r="R137" s="81"/>
-      <c r="S137" s="81"/>
-      <c r="T137" s="81"/>
-      <c r="U137" s="81"/>
-      <c r="V137" s="81"/>
-      <c r="W137" s="81"/>
-      <c r="X137" s="81"/>
-      <c r="Y137" s="81"/>
+      <c r="D137" s="80"/>
+      <c r="E137" s="80"/>
+      <c r="F137" s="80"/>
+      <c r="G137" s="80"/>
+      <c r="H137" s="80"/>
+      <c r="I137" s="80"/>
+      <c r="J137" s="80"/>
+      <c r="K137" s="80"/>
+      <c r="L137" s="80"/>
+      <c r="M137" s="80"/>
+      <c r="N137" s="80"/>
+      <c r="O137" s="80"/>
+      <c r="P137" s="80"/>
+      <c r="Q137" s="80"/>
+      <c r="R137" s="80"/>
+      <c r="S137" s="80"/>
+      <c r="T137" s="80"/>
+      <c r="U137" s="80"/>
+      <c r="V137" s="80"/>
+      <c r="W137" s="80"/>
+      <c r="X137" s="80"/>
+      <c r="Y137" s="80"/>
     </row>
     <row r="138" spans="2:25">
-      <c r="D138" s="81"/>
-      <c r="E138" s="81"/>
-      <c r="F138" s="81"/>
-      <c r="G138" s="81"/>
-      <c r="H138" s="81"/>
-      <c r="I138" s="81"/>
-      <c r="J138" s="81"/>
-      <c r="K138" s="81"/>
-      <c r="L138" s="81"/>
-      <c r="M138" s="81"/>
-      <c r="N138" s="81"/>
-      <c r="O138" s="81"/>
-      <c r="P138" s="81"/>
-      <c r="Q138" s="81"/>
-      <c r="R138" s="81"/>
-      <c r="S138" s="81"/>
-      <c r="T138" s="81"/>
-      <c r="U138" s="81"/>
-      <c r="V138" s="81"/>
-      <c r="W138" s="81"/>
-      <c r="X138" s="81"/>
-      <c r="Y138" s="81"/>
+      <c r="D138" s="80"/>
+      <c r="E138" s="80"/>
+      <c r="F138" s="80"/>
+      <c r="G138" s="80"/>
+      <c r="H138" s="80"/>
+      <c r="I138" s="80"/>
+      <c r="J138" s="80"/>
+      <c r="K138" s="80"/>
+      <c r="L138" s="80"/>
+      <c r="M138" s="80"/>
+      <c r="N138" s="80"/>
+      <c r="O138" s="80"/>
+      <c r="P138" s="80"/>
+      <c r="Q138" s="80"/>
+      <c r="R138" s="80"/>
+      <c r="S138" s="80"/>
+      <c r="T138" s="80"/>
+      <c r="U138" s="80"/>
+      <c r="V138" s="80"/>
+      <c r="W138" s="80"/>
+      <c r="X138" s="80"/>
+      <c r="Y138" s="80"/>
     </row>
     <row r="139" spans="2:25">
-      <c r="D139" s="81"/>
-      <c r="E139" s="81"/>
-      <c r="F139" s="81"/>
-      <c r="G139" s="81"/>
-      <c r="H139" s="81"/>
-      <c r="I139" s="81"/>
-      <c r="J139" s="81"/>
-      <c r="K139" s="81"/>
-      <c r="L139" s="81"/>
-      <c r="M139" s="81"/>
-      <c r="N139" s="81"/>
-      <c r="O139" s="81"/>
-      <c r="P139" s="81"/>
-      <c r="Q139" s="81"/>
-      <c r="R139" s="81"/>
-      <c r="S139" s="81"/>
-      <c r="T139" s="81"/>
-      <c r="U139" s="81"/>
-      <c r="V139" s="81"/>
-      <c r="W139" s="81"/>
-      <c r="X139" s="81"/>
-      <c r="Y139" s="81"/>
+      <c r="D139" s="80"/>
+      <c r="E139" s="80"/>
+      <c r="F139" s="80"/>
+      <c r="G139" s="80"/>
+      <c r="H139" s="80"/>
+      <c r="I139" s="80"/>
+      <c r="J139" s="80"/>
+      <c r="K139" s="80"/>
+      <c r="L139" s="80"/>
+      <c r="M139" s="80"/>
+      <c r="N139" s="80"/>
+      <c r="O139" s="80"/>
+      <c r="P139" s="80"/>
+      <c r="Q139" s="80"/>
+      <c r="R139" s="80"/>
+      <c r="S139" s="80"/>
+      <c r="T139" s="80"/>
+      <c r="U139" s="80"/>
+      <c r="V139" s="80"/>
+      <c r="W139" s="80"/>
+      <c r="X139" s="80"/>
+      <c r="Y139" s="80"/>
     </row>
     <row r="140" spans="2:25">
       <c r="C140" s="29" t="s">
@@ -12409,103 +12431,103 @@
       <c r="C142" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D142" s="81" t="s">
+      <c r="D142" s="80" t="s">
         <v>150</v>
       </c>
-      <c r="E142" s="81"/>
-      <c r="F142" s="81"/>
-      <c r="G142" s="81"/>
-      <c r="H142" s="81"/>
-      <c r="I142" s="81"/>
-      <c r="J142" s="81"/>
-      <c r="K142" s="81"/>
-      <c r="L142" s="81"/>
-      <c r="M142" s="81"/>
-      <c r="N142" s="81"/>
-      <c r="O142" s="81"/>
-      <c r="P142" s="81"/>
-      <c r="Q142" s="81"/>
-      <c r="R142" s="81"/>
-      <c r="S142" s="81"/>
-      <c r="T142" s="81"/>
-      <c r="U142" s="81"/>
-      <c r="V142" s="81"/>
-      <c r="W142" s="81"/>
-      <c r="X142" s="81"/>
-      <c r="Y142" s="81"/>
+      <c r="E142" s="80"/>
+      <c r="F142" s="80"/>
+      <c r="G142" s="80"/>
+      <c r="H142" s="80"/>
+      <c r="I142" s="80"/>
+      <c r="J142" s="80"/>
+      <c r="K142" s="80"/>
+      <c r="L142" s="80"/>
+      <c r="M142" s="80"/>
+      <c r="N142" s="80"/>
+      <c r="O142" s="80"/>
+      <c r="P142" s="80"/>
+      <c r="Q142" s="80"/>
+      <c r="R142" s="80"/>
+      <c r="S142" s="80"/>
+      <c r="T142" s="80"/>
+      <c r="U142" s="80"/>
+      <c r="V142" s="80"/>
+      <c r="W142" s="80"/>
+      <c r="X142" s="80"/>
+      <c r="Y142" s="80"/>
     </row>
     <row r="143" spans="2:25">
       <c r="C143" s="29"/>
-      <c r="D143" s="81"/>
-      <c r="E143" s="81"/>
-      <c r="F143" s="81"/>
-      <c r="G143" s="81"/>
-      <c r="H143" s="81"/>
-      <c r="I143" s="81"/>
-      <c r="J143" s="81"/>
-      <c r="K143" s="81"/>
-      <c r="L143" s="81"/>
-      <c r="M143" s="81"/>
-      <c r="N143" s="81"/>
-      <c r="O143" s="81"/>
-      <c r="P143" s="81"/>
-      <c r="Q143" s="81"/>
-      <c r="R143" s="81"/>
-      <c r="S143" s="81"/>
-      <c r="T143" s="81"/>
-      <c r="U143" s="81"/>
-      <c r="V143" s="81"/>
-      <c r="W143" s="81"/>
-      <c r="X143" s="81"/>
-      <c r="Y143" s="81"/>
+      <c r="D143" s="80"/>
+      <c r="E143" s="80"/>
+      <c r="F143" s="80"/>
+      <c r="G143" s="80"/>
+      <c r="H143" s="80"/>
+      <c r="I143" s="80"/>
+      <c r="J143" s="80"/>
+      <c r="K143" s="80"/>
+      <c r="L143" s="80"/>
+      <c r="M143" s="80"/>
+      <c r="N143" s="80"/>
+      <c r="O143" s="80"/>
+      <c r="P143" s="80"/>
+      <c r="Q143" s="80"/>
+      <c r="R143" s="80"/>
+      <c r="S143" s="80"/>
+      <c r="T143" s="80"/>
+      <c r="U143" s="80"/>
+      <c r="V143" s="80"/>
+      <c r="W143" s="80"/>
+      <c r="X143" s="80"/>
+      <c r="Y143" s="80"/>
     </row>
     <row r="144" spans="2:25">
-      <c r="D144" s="81"/>
-      <c r="E144" s="81"/>
-      <c r="F144" s="81"/>
-      <c r="G144" s="81"/>
-      <c r="H144" s="81"/>
-      <c r="I144" s="81"/>
-      <c r="J144" s="81"/>
-      <c r="K144" s="81"/>
-      <c r="L144" s="81"/>
-      <c r="M144" s="81"/>
-      <c r="N144" s="81"/>
-      <c r="O144" s="81"/>
-      <c r="P144" s="81"/>
-      <c r="Q144" s="81"/>
-      <c r="R144" s="81"/>
-      <c r="S144" s="81"/>
-      <c r="T144" s="81"/>
-      <c r="U144" s="81"/>
-      <c r="V144" s="81"/>
-      <c r="W144" s="81"/>
-      <c r="X144" s="81"/>
-      <c r="Y144" s="81"/>
+      <c r="D144" s="80"/>
+      <c r="E144" s="80"/>
+      <c r="F144" s="80"/>
+      <c r="G144" s="80"/>
+      <c r="H144" s="80"/>
+      <c r="I144" s="80"/>
+      <c r="J144" s="80"/>
+      <c r="K144" s="80"/>
+      <c r="L144" s="80"/>
+      <c r="M144" s="80"/>
+      <c r="N144" s="80"/>
+      <c r="O144" s="80"/>
+      <c r="P144" s="80"/>
+      <c r="Q144" s="80"/>
+      <c r="R144" s="80"/>
+      <c r="S144" s="80"/>
+      <c r="T144" s="80"/>
+      <c r="U144" s="80"/>
+      <c r="V144" s="80"/>
+      <c r="W144" s="80"/>
+      <c r="X144" s="80"/>
+      <c r="Y144" s="80"/>
     </row>
     <row r="145" spans="2:26">
-      <c r="D145" s="81"/>
-      <c r="E145" s="81"/>
-      <c r="F145" s="81"/>
-      <c r="G145" s="81"/>
-      <c r="H145" s="81"/>
-      <c r="I145" s="81"/>
-      <c r="J145" s="81"/>
-      <c r="K145" s="81"/>
-      <c r="L145" s="81"/>
-      <c r="M145" s="81"/>
-      <c r="N145" s="81"/>
-      <c r="O145" s="81"/>
-      <c r="P145" s="81"/>
-      <c r="Q145" s="81"/>
-      <c r="R145" s="81"/>
-      <c r="S145" s="81"/>
-      <c r="T145" s="81"/>
-      <c r="U145" s="81"/>
-      <c r="V145" s="81"/>
-      <c r="W145" s="81"/>
-      <c r="X145" s="81"/>
-      <c r="Y145" s="81"/>
+      <c r="D145" s="80"/>
+      <c r="E145" s="80"/>
+      <c r="F145" s="80"/>
+      <c r="G145" s="80"/>
+      <c r="H145" s="80"/>
+      <c r="I145" s="80"/>
+      <c r="J145" s="80"/>
+      <c r="K145" s="80"/>
+      <c r="L145" s="80"/>
+      <c r="M145" s="80"/>
+      <c r="N145" s="80"/>
+      <c r="O145" s="80"/>
+      <c r="P145" s="80"/>
+      <c r="Q145" s="80"/>
+      <c r="R145" s="80"/>
+      <c r="S145" s="80"/>
+      <c r="T145" s="80"/>
+      <c r="U145" s="80"/>
+      <c r="V145" s="80"/>
+      <c r="W145" s="80"/>
+      <c r="X145" s="80"/>
+      <c r="Y145" s="80"/>
     </row>
     <row r="146" spans="2:26">
       <c r="D146" s="1" t="s">
@@ -12527,78 +12549,78 @@
     </row>
     <row r="149" spans="2:26">
       <c r="C149" s="29"/>
-      <c r="D149" s="80" t="s">
+      <c r="D149" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="E149" s="80"/>
-      <c r="F149" s="80"/>
-      <c r="G149" s="80"/>
-      <c r="H149" s="80"/>
-      <c r="I149" s="80"/>
-      <c r="J149" s="80"/>
-      <c r="K149" s="80"/>
-      <c r="L149" s="80"/>
-      <c r="M149" s="80"/>
-      <c r="N149" s="80"/>
-      <c r="O149" s="80"/>
-      <c r="P149" s="80"/>
-      <c r="Q149" s="80"/>
-      <c r="R149" s="80"/>
-      <c r="S149" s="80"/>
-      <c r="T149" s="80"/>
-      <c r="U149" s="80"/>
-      <c r="V149" s="80"/>
-      <c r="W149" s="80"/>
-      <c r="X149" s="80"/>
-      <c r="Y149" s="80"/>
+      <c r="E149" s="81"/>
+      <c r="F149" s="81"/>
+      <c r="G149" s="81"/>
+      <c r="H149" s="81"/>
+      <c r="I149" s="81"/>
+      <c r="J149" s="81"/>
+      <c r="K149" s="81"/>
+      <c r="L149" s="81"/>
+      <c r="M149" s="81"/>
+      <c r="N149" s="81"/>
+      <c r="O149" s="81"/>
+      <c r="P149" s="81"/>
+      <c r="Q149" s="81"/>
+      <c r="R149" s="81"/>
+      <c r="S149" s="81"/>
+      <c r="T149" s="81"/>
+      <c r="U149" s="81"/>
+      <c r="V149" s="81"/>
+      <c r="W149" s="81"/>
+      <c r="X149" s="81"/>
+      <c r="Y149" s="81"/>
     </row>
     <row r="150" spans="2:26">
-      <c r="D150" s="80"/>
-      <c r="E150" s="80"/>
-      <c r="F150" s="80"/>
-      <c r="G150" s="80"/>
-      <c r="H150" s="80"/>
-      <c r="I150" s="80"/>
-      <c r="J150" s="80"/>
-      <c r="K150" s="80"/>
-      <c r="L150" s="80"/>
-      <c r="M150" s="80"/>
-      <c r="N150" s="80"/>
-      <c r="O150" s="80"/>
-      <c r="P150" s="80"/>
-      <c r="Q150" s="80"/>
-      <c r="R150" s="80"/>
-      <c r="S150" s="80"/>
-      <c r="T150" s="80"/>
-      <c r="U150" s="80"/>
-      <c r="V150" s="80"/>
-      <c r="W150" s="80"/>
-      <c r="X150" s="80"/>
-      <c r="Y150" s="80"/>
+      <c r="D150" s="81"/>
+      <c r="E150" s="81"/>
+      <c r="F150" s="81"/>
+      <c r="G150" s="81"/>
+      <c r="H150" s="81"/>
+      <c r="I150" s="81"/>
+      <c r="J150" s="81"/>
+      <c r="K150" s="81"/>
+      <c r="L150" s="81"/>
+      <c r="M150" s="81"/>
+      <c r="N150" s="81"/>
+      <c r="O150" s="81"/>
+      <c r="P150" s="81"/>
+      <c r="Q150" s="81"/>
+      <c r="R150" s="81"/>
+      <c r="S150" s="81"/>
+      <c r="T150" s="81"/>
+      <c r="U150" s="81"/>
+      <c r="V150" s="81"/>
+      <c r="W150" s="81"/>
+      <c r="X150" s="81"/>
+      <c r="Y150" s="81"/>
     </row>
     <row r="151" spans="2:26">
-      <c r="D151" s="80"/>
-      <c r="E151" s="80"/>
-      <c r="F151" s="80"/>
-      <c r="G151" s="80"/>
-      <c r="H151" s="80"/>
-      <c r="I151" s="80"/>
-      <c r="J151" s="80"/>
-      <c r="K151" s="80"/>
-      <c r="L151" s="80"/>
-      <c r="M151" s="80"/>
-      <c r="N151" s="80"/>
-      <c r="O151" s="80"/>
-      <c r="P151" s="80"/>
-      <c r="Q151" s="80"/>
-      <c r="R151" s="80"/>
-      <c r="S151" s="80"/>
-      <c r="T151" s="80"/>
-      <c r="U151" s="80"/>
-      <c r="V151" s="80"/>
-      <c r="W151" s="80"/>
-      <c r="X151" s="80"/>
-      <c r="Y151" s="80"/>
+      <c r="D151" s="81"/>
+      <c r="E151" s="81"/>
+      <c r="F151" s="81"/>
+      <c r="G151" s="81"/>
+      <c r="H151" s="81"/>
+      <c r="I151" s="81"/>
+      <c r="J151" s="81"/>
+      <c r="K151" s="81"/>
+      <c r="L151" s="81"/>
+      <c r="M151" s="81"/>
+      <c r="N151" s="81"/>
+      <c r="O151" s="81"/>
+      <c r="P151" s="81"/>
+      <c r="Q151" s="81"/>
+      <c r="R151" s="81"/>
+      <c r="S151" s="81"/>
+      <c r="T151" s="81"/>
+      <c r="U151" s="81"/>
+      <c r="V151" s="81"/>
+      <c r="W151" s="81"/>
+      <c r="X151" s="81"/>
+      <c r="Y151" s="81"/>
     </row>
     <row r="152" spans="2:26">
       <c r="B152" s="1" t="s">
@@ -12606,56 +12628,56 @@
       </c>
     </row>
     <row r="153" spans="2:26" ht="14.25" customHeight="1">
-      <c r="D153" s="81" t="s">
+      <c r="D153" s="80" t="s">
         <v>156</v>
       </c>
-      <c r="E153" s="81"/>
-      <c r="F153" s="81"/>
-      <c r="G153" s="81"/>
-      <c r="H153" s="81"/>
-      <c r="I153" s="81"/>
-      <c r="J153" s="81"/>
-      <c r="K153" s="81"/>
-      <c r="L153" s="81"/>
-      <c r="M153" s="81"/>
-      <c r="N153" s="81"/>
-      <c r="O153" s="81"/>
-      <c r="P153" s="81"/>
-      <c r="Q153" s="81"/>
-      <c r="R153" s="81"/>
-      <c r="S153" s="81"/>
-      <c r="T153" s="81"/>
-      <c r="U153" s="81"/>
-      <c r="V153" s="81"/>
-      <c r="W153" s="81"/>
-      <c r="X153" s="81"/>
-      <c r="Y153" s="81"/>
-      <c r="Z153" s="81"/>
+      <c r="E153" s="80"/>
+      <c r="F153" s="80"/>
+      <c r="G153" s="80"/>
+      <c r="H153" s="80"/>
+      <c r="I153" s="80"/>
+      <c r="J153" s="80"/>
+      <c r="K153" s="80"/>
+      <c r="L153" s="80"/>
+      <c r="M153" s="80"/>
+      <c r="N153" s="80"/>
+      <c r="O153" s="80"/>
+      <c r="P153" s="80"/>
+      <c r="Q153" s="80"/>
+      <c r="R153" s="80"/>
+      <c r="S153" s="80"/>
+      <c r="T153" s="80"/>
+      <c r="U153" s="80"/>
+      <c r="V153" s="80"/>
+      <c r="W153" s="80"/>
+      <c r="X153" s="80"/>
+      <c r="Y153" s="80"/>
+      <c r="Z153" s="80"/>
     </row>
     <row r="154" spans="2:26">
-      <c r="D154" s="81"/>
-      <c r="E154" s="81"/>
-      <c r="F154" s="81"/>
-      <c r="G154" s="81"/>
-      <c r="H154" s="81"/>
-      <c r="I154" s="81"/>
-      <c r="J154" s="81"/>
-      <c r="K154" s="81"/>
-      <c r="L154" s="81"/>
-      <c r="M154" s="81"/>
-      <c r="N154" s="81"/>
-      <c r="O154" s="81"/>
-      <c r="P154" s="81"/>
-      <c r="Q154" s="81"/>
-      <c r="R154" s="81"/>
-      <c r="S154" s="81"/>
-      <c r="T154" s="81"/>
-      <c r="U154" s="81"/>
-      <c r="V154" s="81"/>
-      <c r="W154" s="81"/>
-      <c r="X154" s="81"/>
-      <c r="Y154" s="81"/>
-      <c r="Z154" s="81"/>
+      <c r="D154" s="80"/>
+      <c r="E154" s="80"/>
+      <c r="F154" s="80"/>
+      <c r="G154" s="80"/>
+      <c r="H154" s="80"/>
+      <c r="I154" s="80"/>
+      <c r="J154" s="80"/>
+      <c r="K154" s="80"/>
+      <c r="L154" s="80"/>
+      <c r="M154" s="80"/>
+      <c r="N154" s="80"/>
+      <c r="O154" s="80"/>
+      <c r="P154" s="80"/>
+      <c r="Q154" s="80"/>
+      <c r="R154" s="80"/>
+      <c r="S154" s="80"/>
+      <c r="T154" s="80"/>
+      <c r="U154" s="80"/>
+      <c r="V154" s="80"/>
+      <c r="W154" s="80"/>
+      <c r="X154" s="80"/>
+      <c r="Y154" s="80"/>
+      <c r="Z154" s="80"/>
     </row>
     <row r="155" spans="2:26">
       <c r="D155" s="56"/>
@@ -12683,6 +12705,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D94:Y95"/>
+    <mergeCell ref="D96:Y97"/>
+    <mergeCell ref="D101:Y102"/>
+    <mergeCell ref="D103:Y104"/>
+    <mergeCell ref="D86:Y89"/>
+    <mergeCell ref="D90:Y92"/>
+    <mergeCell ref="Z108:AV109"/>
+    <mergeCell ref="D108:Y109"/>
+    <mergeCell ref="D117:Y120"/>
+    <mergeCell ref="D121:Y122"/>
+    <mergeCell ref="D123:Z124"/>
     <mergeCell ref="D136:Y139"/>
     <mergeCell ref="D142:Y145"/>
     <mergeCell ref="D149:Y151"/>
@@ -12690,17 +12723,6 @@
     <mergeCell ref="D125:AA127"/>
     <mergeCell ref="D128:Y129"/>
     <mergeCell ref="D132:Y134"/>
-    <mergeCell ref="Z108:AV109"/>
-    <mergeCell ref="D108:Y109"/>
-    <mergeCell ref="D117:Y120"/>
-    <mergeCell ref="D121:Y122"/>
-    <mergeCell ref="D123:Z124"/>
-    <mergeCell ref="D94:Y95"/>
-    <mergeCell ref="D96:Y97"/>
-    <mergeCell ref="D101:Y102"/>
-    <mergeCell ref="D103:Y104"/>
-    <mergeCell ref="D86:Y89"/>
-    <mergeCell ref="D90:Y92"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="R11" r:id="rId1" xr:uid="{3A32E811-E794-46FB-A010-EBB0450F323B}"/>
